--- a/Carbon/d13C_Sediment.xlsx
+++ b/Carbon/d13C_Sediment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lukaseamus/Desktop/PhD/Papers/Burial/kelp-burial/Carbon/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDF62AC5-5C5A-244A-B0EB-52F6ECDF44EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4962F0F1-38CD-9D41-B510-01959D0BCA12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19020" xr2:uid="{D120C0EF-290F-244A-AE4B-CB2F7CD281C3}"/>
+    <workbookView xWindow="120" yWindow="660" windowWidth="18980" windowHeight="18720" xr2:uid="{D120C0EF-290F-244A-AE4B-CB2F7CD281C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1687" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1690" uniqueCount="532">
   <si>
     <t>ID</t>
   </si>
@@ -254,9 +254,6 @@
     <t>L_1_2_2</t>
   </si>
   <si>
-    <t>L_2_3_2</t>
-  </si>
-  <si>
     <t>L_2_2_2</t>
   </si>
   <si>
@@ -1629,6 +1626,12 @@
   </si>
   <si>
     <t>C</t>
+  </si>
+  <si>
+    <t>E_1_13_8</t>
+  </si>
+  <si>
+    <t>L_2_1_2</t>
   </si>
 </sst>
 </file>
@@ -2014,7 +2017,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18AC6222-1A29-714F-879C-A900060CD8DA}">
-  <dimension ref="A1:N561"/>
+  <dimension ref="A1:N562"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.5" customWidth="1"/>
@@ -2033,7 +2036,7 @@
         <v>16</v>
       </c>
       <c r="D1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E1" t="s">
         <v>15</v>
@@ -3959,7 +3962,7 @@
         <v>26</v>
       </c>
       <c r="B85" t="s">
-        <v>72</v>
+        <v>531</v>
       </c>
       <c r="C85">
         <v>5.1470000000000002</v>
@@ -3982,7 +3985,7 @@
         <v>26</v>
       </c>
       <c r="B86" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C86">
         <v>5.1130000000000004</v>
@@ -4005,7 +4008,7 @@
         <v>26</v>
       </c>
       <c r="B87" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C87">
         <v>5.3739999999999997</v>
@@ -4051,7 +4054,7 @@
         <v>26</v>
       </c>
       <c r="B89" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C89">
         <v>5.4829999999999997</v>
@@ -4097,7 +4100,7 @@
         <v>26</v>
       </c>
       <c r="B91" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C91">
         <v>5.1820000000000004</v>
@@ -4120,7 +4123,7 @@
         <v>26</v>
       </c>
       <c r="B92" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C92">
         <v>5.17</v>
@@ -4166,7 +4169,7 @@
         <v>26</v>
       </c>
       <c r="B94" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C94">
         <v>5.4889999999999999</v>
@@ -4189,7 +4192,7 @@
         <v>26</v>
       </c>
       <c r="B95" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C95">
         <v>5.3460000000000001</v>
@@ -4212,7 +4215,7 @@
         <v>26</v>
       </c>
       <c r="B96" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C96">
         <v>5.4189999999999996</v>
@@ -4235,7 +4238,7 @@
         <v>26</v>
       </c>
       <c r="B97" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C97">
         <v>5.0259999999999998</v>
@@ -4258,7 +4261,7 @@
         <v>26</v>
       </c>
       <c r="B98" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C98">
         <v>5.2610000000000001</v>
@@ -4281,7 +4284,7 @@
         <v>26</v>
       </c>
       <c r="B99" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C99">
         <v>5.4489999999999998</v>
@@ -4304,7 +4307,7 @@
         <v>26</v>
       </c>
       <c r="B100" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C100">
         <v>5.0270000000000001</v>
@@ -4327,7 +4330,7 @@
         <v>26</v>
       </c>
       <c r="B101" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C101">
         <v>5.4660000000000002</v>
@@ -4350,7 +4353,7 @@
         <v>26</v>
       </c>
       <c r="B102" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C102">
         <v>5.1920000000000002</v>
@@ -4373,7 +4376,7 @@
         <v>26</v>
       </c>
       <c r="B103" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C103">
         <v>5.17</v>
@@ -4396,7 +4399,7 @@
         <v>26</v>
       </c>
       <c r="B104" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C104">
         <v>5.15</v>
@@ -4419,7 +4422,7 @@
         <v>26</v>
       </c>
       <c r="B105" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C105">
         <v>5.3369999999999997</v>
@@ -4465,7 +4468,7 @@
         <v>26</v>
       </c>
       <c r="B107" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C107">
         <v>5.2519999999999998</v>
@@ -4488,7 +4491,7 @@
         <v>26</v>
       </c>
       <c r="B108" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C108">
         <v>5.2210000000000001</v>
@@ -4511,7 +4514,7 @@
         <v>26</v>
       </c>
       <c r="B109" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C109">
         <v>5.3490000000000002</v>
@@ -4534,7 +4537,7 @@
         <v>26</v>
       </c>
       <c r="B110" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C110">
         <v>5.069</v>
@@ -4557,7 +4560,7 @@
         <v>26</v>
       </c>
       <c r="B111" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C111">
         <v>5.3040000000000003</v>
@@ -4580,7 +4583,7 @@
         <v>26</v>
       </c>
       <c r="B112" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C112">
         <v>5.19</v>
@@ -4603,7 +4606,7 @@
         <v>26</v>
       </c>
       <c r="B113" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C113">
         <v>5.1660000000000004</v>
@@ -4626,7 +4629,7 @@
         <v>26</v>
       </c>
       <c r="B114" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C114">
         <v>5.25</v>
@@ -4649,7 +4652,7 @@
         <v>26</v>
       </c>
       <c r="B115" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C115">
         <v>5.1100000000000003</v>
@@ -4672,7 +4675,7 @@
         <v>26</v>
       </c>
       <c r="B116" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C116">
         <v>5.2</v>
@@ -4695,7 +4698,7 @@
         <v>26</v>
       </c>
       <c r="B117" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C117">
         <v>5.3609999999999998</v>
@@ -4718,7 +4721,7 @@
         <v>26</v>
       </c>
       <c r="B118" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C118">
         <v>5.306</v>
@@ -4741,7 +4744,7 @@
         <v>26</v>
       </c>
       <c r="B119" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C119">
         <v>5.0339999999999998</v>
@@ -4764,7 +4767,7 @@
         <v>26</v>
       </c>
       <c r="B120" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C120">
         <v>5.141</v>
@@ -4787,7 +4790,7 @@
         <v>26</v>
       </c>
       <c r="B121" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C121">
         <v>5.5</v>
@@ -4810,7 +4813,7 @@
         <v>26</v>
       </c>
       <c r="B122" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C122">
         <v>5.0190000000000001</v>
@@ -4833,7 +4836,7 @@
         <v>26</v>
       </c>
       <c r="B123" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C123">
         <v>5.0270000000000001</v>
@@ -4856,7 +4859,7 @@
         <v>26</v>
       </c>
       <c r="B124" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C124">
         <v>5.0439999999999996</v>
@@ -4879,7 +4882,7 @@
         <v>26</v>
       </c>
       <c r="B125" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C125">
         <v>5.37</v>
@@ -4902,7 +4905,7 @@
         <v>26</v>
       </c>
       <c r="B126" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C126">
         <v>5.3150000000000004</v>
@@ -4925,7 +4928,7 @@
         <v>26</v>
       </c>
       <c r="B127" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C127">
         <v>5.2039999999999997</v>
@@ -4948,7 +4951,7 @@
         <v>26</v>
       </c>
       <c r="B128" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C128">
         <v>5.468</v>
@@ -4971,7 +4974,7 @@
         <v>26</v>
       </c>
       <c r="B129" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C129">
         <v>5.258</v>
@@ -4994,7 +4997,7 @@
         <v>26</v>
       </c>
       <c r="B130" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C130">
         <v>5.1890000000000001</v>
@@ -5017,7 +5020,7 @@
         <v>26</v>
       </c>
       <c r="B131" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C131">
         <v>5.3979999999999997</v>
@@ -5040,7 +5043,7 @@
         <v>26</v>
       </c>
       <c r="B132" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C132">
         <v>5.0090000000000003</v>
@@ -5063,7 +5066,7 @@
         <v>26</v>
       </c>
       <c r="B133" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C133">
         <v>5.2210000000000001</v>
@@ -5086,7 +5089,7 @@
         <v>26</v>
       </c>
       <c r="B134" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C134">
         <v>5.3109999999999999</v>
@@ -5109,7 +5112,7 @@
         <v>26</v>
       </c>
       <c r="B135" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C135">
         <v>5.4820000000000002</v>
@@ -5132,7 +5135,7 @@
         <v>26</v>
       </c>
       <c r="B136" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C136">
         <v>5.468</v>
@@ -5155,7 +5158,7 @@
         <v>26</v>
       </c>
       <c r="B137" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C137">
         <v>5.0839999999999996</v>
@@ -5178,7 +5181,7 @@
         <v>26</v>
       </c>
       <c r="B138" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C138">
         <v>5.0910000000000002</v>
@@ -5201,7 +5204,7 @@
         <v>26</v>
       </c>
       <c r="B139" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C139">
         <v>5.0759999999999996</v>
@@ -5224,7 +5227,7 @@
         <v>26</v>
       </c>
       <c r="B140" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C140">
         <v>5.1589999999999998</v>
@@ -5247,7 +5250,7 @@
         <v>26</v>
       </c>
       <c r="B141" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C141">
         <v>5.2690000000000001</v>
@@ -5270,7 +5273,7 @@
         <v>26</v>
       </c>
       <c r="B142" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C142">
         <v>5.0890000000000004</v>
@@ -5293,7 +5296,7 @@
         <v>26</v>
       </c>
       <c r="B143" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C143">
         <v>5.0869999999999997</v>
@@ -5316,7 +5319,7 @@
         <v>26</v>
       </c>
       <c r="B144" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C144">
         <v>5.0460000000000003</v>
@@ -5339,7 +5342,7 @@
         <v>26</v>
       </c>
       <c r="B145" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C145">
         <v>5.4119999999999999</v>
@@ -5362,7 +5365,7 @@
         <v>26</v>
       </c>
       <c r="B146" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C146">
         <v>5.218</v>
@@ -5385,7 +5388,7 @@
         <v>26</v>
       </c>
       <c r="B147" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C147">
         <v>5.415</v>
@@ -5408,7 +5411,7 @@
         <v>26</v>
       </c>
       <c r="B148" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C148">
         <v>5.3129999999999997</v>
@@ -5431,7 +5434,7 @@
         <v>26</v>
       </c>
       <c r="B149" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C149">
         <v>5.1050000000000004</v>
@@ -5454,7 +5457,7 @@
         <v>26</v>
       </c>
       <c r="B150" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C150">
         <v>5.4009999999999998</v>
@@ -5477,7 +5480,7 @@
         <v>26</v>
       </c>
       <c r="B151" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C151">
         <v>5.1550000000000002</v>
@@ -5500,7 +5503,7 @@
         <v>26</v>
       </c>
       <c r="B152" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C152">
         <v>5.26</v>
@@ -5523,7 +5526,7 @@
         <v>26</v>
       </c>
       <c r="B153" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C153">
         <v>5.2779999999999996</v>
@@ -5546,7 +5549,7 @@
         <v>26</v>
       </c>
       <c r="B154" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C154">
         <v>5.0439999999999996</v>
@@ -5569,7 +5572,7 @@
         <v>26</v>
       </c>
       <c r="B155" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C155">
         <v>5.101</v>
@@ -5592,7 +5595,7 @@
         <v>26</v>
       </c>
       <c r="B156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C156">
         <v>5.4630000000000001</v>
@@ -5615,7 +5618,7 @@
         <v>26</v>
       </c>
       <c r="B157" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C157">
         <v>5.3410000000000002</v>
@@ -5638,7 +5641,7 @@
         <v>26</v>
       </c>
       <c r="B158" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C158">
         <v>5.1710000000000003</v>
@@ -5661,7 +5664,7 @@
         <v>26</v>
       </c>
       <c r="B159" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C159">
         <v>5.0789999999999997</v>
@@ -5707,7 +5710,7 @@
         <v>26</v>
       </c>
       <c r="B161" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C161">
         <v>5.4459999999999997</v>
@@ -5753,7 +5756,7 @@
         <v>26</v>
       </c>
       <c r="B163" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C163">
         <v>5.3079999999999998</v>
@@ -5776,7 +5779,7 @@
         <v>26</v>
       </c>
       <c r="B164" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C164">
         <v>5.2640000000000002</v>
@@ -5799,7 +5802,7 @@
         <v>26</v>
       </c>
       <c r="B165" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C165">
         <v>5.2320000000000002</v>
@@ -5822,7 +5825,7 @@
         <v>26</v>
       </c>
       <c r="B166" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C166">
         <v>5.4939999999999998</v>
@@ -5845,7 +5848,7 @@
         <v>26</v>
       </c>
       <c r="B167" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C167">
         <v>5.3120000000000003</v>
@@ -5868,7 +5871,7 @@
         <v>26</v>
       </c>
       <c r="B168" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C168">
         <v>5.3029999999999999</v>
@@ -5891,7 +5894,7 @@
         <v>26</v>
       </c>
       <c r="B169" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C169">
         <v>5.3330000000000002</v>
@@ -5914,7 +5917,7 @@
         <v>26</v>
       </c>
       <c r="B170" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C170">
         <v>5.1159999999999997</v>
@@ -5937,7 +5940,7 @@
         <v>26</v>
       </c>
       <c r="B171" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C171">
         <v>5.133</v>
@@ -5960,7 +5963,7 @@
         <v>26</v>
       </c>
       <c r="B172" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C172">
         <v>5.0330000000000004</v>
@@ -5983,7 +5986,7 @@
         <v>26</v>
       </c>
       <c r="B173" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C173">
         <v>5.0810000000000004</v>
@@ -6006,7 +6009,7 @@
         <v>26</v>
       </c>
       <c r="B174" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C174">
         <v>5.1619999999999999</v>
@@ -6029,7 +6032,7 @@
         <v>26</v>
       </c>
       <c r="B175" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C175">
         <v>5.3869999999999996</v>
@@ -6052,7 +6055,7 @@
         <v>26</v>
       </c>
       <c r="B176" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C176">
         <v>5.2519999999999998</v>
@@ -6075,7 +6078,7 @@
         <v>26</v>
       </c>
       <c r="B177" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C177">
         <v>5.1269999999999998</v>
@@ -6098,7 +6101,7 @@
         <v>26</v>
       </c>
       <c r="B178" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C178">
         <v>5.0510000000000002</v>
@@ -6121,7 +6124,7 @@
         <v>26</v>
       </c>
       <c r="B179" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C179">
         <v>5.1669999999999998</v>
@@ -6144,7 +6147,7 @@
         <v>26</v>
       </c>
       <c r="B180" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C180">
         <v>5.27</v>
@@ -6167,7 +6170,7 @@
         <v>26</v>
       </c>
       <c r="B181" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C181">
         <v>5.319</v>
@@ -6190,7 +6193,7 @@
         <v>26</v>
       </c>
       <c r="B182" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C182">
         <v>5.4649999999999999</v>
@@ -6213,7 +6216,7 @@
         <v>26</v>
       </c>
       <c r="B183" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C183">
         <v>5.3819999999999997</v>
@@ -6236,7 +6239,7 @@
         <v>26</v>
       </c>
       <c r="B184" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C184">
         <v>5.0970000000000004</v>
@@ -6259,7 +6262,7 @@
         <v>26</v>
       </c>
       <c r="B185" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C185">
         <v>5.0839999999999996</v>
@@ -6282,7 +6285,7 @@
         <v>26</v>
       </c>
       <c r="B186" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C186">
         <v>5.1120000000000001</v>
@@ -6305,7 +6308,7 @@
         <v>26</v>
       </c>
       <c r="B187" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C187">
         <v>5.399</v>
@@ -6328,7 +6331,7 @@
         <v>26</v>
       </c>
       <c r="B188" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C188">
         <v>5.1509999999999998</v>
@@ -6351,7 +6354,7 @@
         <v>26</v>
       </c>
       <c r="B189" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C189">
         <v>5.1449999999999996</v>
@@ -6374,7 +6377,7 @@
         <v>26</v>
       </c>
       <c r="B190" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C190">
         <v>5.367</v>
@@ -6397,7 +6400,7 @@
         <v>26</v>
       </c>
       <c r="B191" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C191">
         <v>5.2329999999999997</v>
@@ -6420,7 +6423,7 @@
         <v>26</v>
       </c>
       <c r="B192" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C192">
         <v>5.4660000000000002</v>
@@ -6443,7 +6446,7 @@
         <v>26</v>
       </c>
       <c r="B193" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C193">
         <v>5.024</v>
@@ -6466,7 +6469,7 @@
         <v>26</v>
       </c>
       <c r="B194" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C194">
         <v>5.3769999999999998</v>
@@ -6489,7 +6492,7 @@
         <v>26</v>
       </c>
       <c r="B195" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C195">
         <v>5.2370000000000001</v>
@@ -6512,7 +6515,7 @@
         <v>26</v>
       </c>
       <c r="B196" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C196">
         <v>5.0570000000000004</v>
@@ -6535,7 +6538,7 @@
         <v>26</v>
       </c>
       <c r="B197" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C197">
         <v>5.1909999999999998</v>
@@ -6558,7 +6561,7 @@
         <v>26</v>
       </c>
       <c r="B198" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C198">
         <v>5.3570000000000002</v>
@@ -6581,7 +6584,7 @@
         <v>26</v>
       </c>
       <c r="B199" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C199">
         <v>5.3179999999999996</v>
@@ -6604,7 +6607,7 @@
         <v>26</v>
       </c>
       <c r="B200" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C200">
         <v>5.0890000000000004</v>
@@ -6627,7 +6630,7 @@
         <v>26</v>
       </c>
       <c r="B201" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C201">
         <v>5.3780000000000001</v>
@@ -6650,7 +6653,7 @@
         <v>26</v>
       </c>
       <c r="B202" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C202">
         <v>5.1210000000000004</v>
@@ -6673,7 +6676,7 @@
         <v>26</v>
       </c>
       <c r="B203" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C203">
         <v>5.3470000000000004</v>
@@ -6696,7 +6699,7 @@
         <v>26</v>
       </c>
       <c r="B204" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C204">
         <v>5.2320000000000002</v>
@@ -6719,7 +6722,7 @@
         <v>26</v>
       </c>
       <c r="B205" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C205">
         <v>5.26</v>
@@ -6742,7 +6745,7 @@
         <v>26</v>
       </c>
       <c r="B206" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C206">
         <v>5.0780000000000003</v>
@@ -6765,7 +6768,7 @@
         <v>26</v>
       </c>
       <c r="B207" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C207">
         <v>5.2869999999999999</v>
@@ -6788,7 +6791,7 @@
         <v>26</v>
       </c>
       <c r="B208" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C208">
         <v>5.0119999999999996</v>
@@ -6811,7 +6814,7 @@
         <v>26</v>
       </c>
       <c r="B209" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C209">
         <v>5.1269999999999998</v>
@@ -6834,7 +6837,7 @@
         <v>26</v>
       </c>
       <c r="B210" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C210">
         <v>5.1760000000000002</v>
@@ -6857,7 +6860,7 @@
         <v>26</v>
       </c>
       <c r="B211" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C211">
         <v>5.0880000000000001</v>
@@ -6880,7 +6883,7 @@
         <v>26</v>
       </c>
       <c r="B212" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C212">
         <v>5.3040000000000003</v>
@@ -6903,7 +6906,7 @@
         <v>26</v>
       </c>
       <c r="B213" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C213">
         <v>5.3979999999999997</v>
@@ -6926,7 +6929,7 @@
         <v>26</v>
       </c>
       <c r="B214" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C214">
         <v>5.2830000000000004</v>
@@ -6949,7 +6952,7 @@
         <v>26</v>
       </c>
       <c r="B215" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C215">
         <v>5.2720000000000002</v>
@@ -6972,7 +6975,7 @@
         <v>26</v>
       </c>
       <c r="B216" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C216">
         <v>5.1260000000000003</v>
@@ -6995,7 +6998,7 @@
         <v>26</v>
       </c>
       <c r="B217" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C217">
         <v>5.0629999999999997</v>
@@ -7018,7 +7021,7 @@
         <v>26</v>
       </c>
       <c r="B218" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C218">
         <v>5.4320000000000004</v>
@@ -7041,7 +7044,7 @@
         <v>26</v>
       </c>
       <c r="B219" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C219">
         <v>5.0529999999999999</v>
@@ -7064,7 +7067,7 @@
         <v>26</v>
       </c>
       <c r="B220" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C220">
         <v>5.4470000000000001</v>
@@ -7087,7 +7090,7 @@
         <v>26</v>
       </c>
       <c r="B221" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C221">
         <v>5.0970000000000004</v>
@@ -7110,7 +7113,7 @@
         <v>26</v>
       </c>
       <c r="B222" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C222">
         <v>5.3769999999999998</v>
@@ -7133,7 +7136,7 @@
         <v>26</v>
       </c>
       <c r="B223" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C223">
         <v>5.266</v>
@@ -7156,7 +7159,7 @@
         <v>26</v>
       </c>
       <c r="B224" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C224">
         <v>5.2850000000000001</v>
@@ -7179,7 +7182,7 @@
         <v>26</v>
       </c>
       <c r="B225" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C225">
         <v>5.327</v>
@@ -7202,7 +7205,7 @@
         <v>26</v>
       </c>
       <c r="B226" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C226">
         <v>5.0890000000000004</v>
@@ -7225,7 +7228,7 @@
         <v>26</v>
       </c>
       <c r="B227" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C227">
         <v>5.1909999999999998</v>
@@ -7248,7 +7251,7 @@
         <v>26</v>
       </c>
       <c r="B228" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C228">
         <v>5.1539999999999999</v>
@@ -7271,7 +7274,7 @@
         <v>26</v>
       </c>
       <c r="B229" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C229">
         <v>5.3289999999999997</v>
@@ -7294,7 +7297,7 @@
         <v>26</v>
       </c>
       <c r="B230" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C230">
         <v>5.0069999999999997</v>
@@ -7317,7 +7320,7 @@
         <v>26</v>
       </c>
       <c r="B231" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C231">
         <v>5.4729999999999999</v>
@@ -7340,7 +7343,7 @@
         <v>26</v>
       </c>
       <c r="B232" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C232">
         <v>5.1369999999999996</v>
@@ -7363,7 +7366,7 @@
         <v>26</v>
       </c>
       <c r="B233" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C233">
         <v>5.2510000000000003</v>
@@ -7386,7 +7389,7 @@
         <v>26</v>
       </c>
       <c r="B234" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C234">
         <v>5.4340000000000002</v>
@@ -7409,7 +7412,7 @@
         <v>26</v>
       </c>
       <c r="B235" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C235">
         <v>5.0999999999999996</v>
@@ -7432,7 +7435,7 @@
         <v>26</v>
       </c>
       <c r="B236" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C236">
         <v>5.1689999999999996</v>
@@ -7478,7 +7481,7 @@
         <v>26</v>
       </c>
       <c r="B238" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C238">
         <v>5.3440000000000003</v>
@@ -7501,7 +7504,7 @@
         <v>26</v>
       </c>
       <c r="B239" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C239">
         <v>5.0049999999999999</v>
@@ -7524,7 +7527,7 @@
         <v>26</v>
       </c>
       <c r="B240" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C240">
         <v>5.1820000000000004</v>
@@ -7547,7 +7550,7 @@
         <v>26</v>
       </c>
       <c r="B241" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C241">
         <v>5.1239999999999997</v>
@@ -7570,7 +7573,7 @@
         <v>26</v>
       </c>
       <c r="B242" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C242">
         <v>5.0380000000000003</v>
@@ -7593,7 +7596,7 @@
         <v>26</v>
       </c>
       <c r="B243" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C243">
         <v>5.1109999999999998</v>
@@ -7616,7 +7619,7 @@
         <v>26</v>
       </c>
       <c r="B244" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C244">
         <v>5.2229999999999999</v>
@@ -7639,7 +7642,7 @@
         <v>26</v>
       </c>
       <c r="B245" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C245">
         <v>5.2089999999999996</v>
@@ -7662,7 +7665,7 @@
         <v>26</v>
       </c>
       <c r="B246" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C246">
         <v>5.476</v>
@@ -7685,7 +7688,7 @@
         <v>26</v>
       </c>
       <c r="B247" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C247">
         <v>5.1360000000000001</v>
@@ -7708,7 +7711,7 @@
         <v>26</v>
       </c>
       <c r="B248" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C248">
         <v>5.2220000000000004</v>
@@ -7731,7 +7734,7 @@
         <v>26</v>
       </c>
       <c r="B249" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C249">
         <v>5.3949999999999996</v>
@@ -7754,7 +7757,7 @@
         <v>26</v>
       </c>
       <c r="B250" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C250">
         <v>5.0549999999999997</v>
@@ -7777,7 +7780,7 @@
         <v>26</v>
       </c>
       <c r="B251" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C251">
         <v>5.0090000000000003</v>
@@ -7800,7 +7803,7 @@
         <v>26</v>
       </c>
       <c r="B252" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C252">
         <v>5.3920000000000003</v>
@@ -7823,7 +7826,7 @@
         <v>26</v>
       </c>
       <c r="B253" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C253">
         <v>5.2519999999999998</v>
@@ -7846,7 +7849,7 @@
         <v>26</v>
       </c>
       <c r="B254" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C254">
         <v>5.2930000000000001</v>
@@ -7869,7 +7872,7 @@
         <v>26</v>
       </c>
       <c r="B255" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C255">
         <v>5.38</v>
@@ -7892,7 +7895,7 @@
         <v>26</v>
       </c>
       <c r="B256" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C256">
         <v>5.0209999999999999</v>
@@ -7915,7 +7918,7 @@
         <v>26</v>
       </c>
       <c r="B257" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C257">
         <v>5.1719999999999997</v>
@@ -7938,7 +7941,7 @@
         <v>26</v>
       </c>
       <c r="B258" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C258">
         <v>5.1369999999999996</v>
@@ -7961,7 +7964,7 @@
         <v>26</v>
       </c>
       <c r="B259" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C259">
         <v>5.4669999999999996</v>
@@ -7984,7 +7987,7 @@
         <v>26</v>
       </c>
       <c r="B260" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C260">
         <v>5.2610000000000001</v>
@@ -8007,7 +8010,7 @@
         <v>26</v>
       </c>
       <c r="B261" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C261">
         <v>5.1159999999999997</v>
@@ -8030,7 +8033,7 @@
         <v>26</v>
       </c>
       <c r="B262" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C262">
         <v>5.2969999999999997</v>
@@ -8053,7 +8056,7 @@
         <v>26</v>
       </c>
       <c r="B263" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C263">
         <v>5.306</v>
@@ -8076,7 +8079,7 @@
         <v>26</v>
       </c>
       <c r="B264" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C264">
         <v>5.1959999999999997</v>
@@ -8099,7 +8102,7 @@
         <v>26</v>
       </c>
       <c r="B265" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C265">
         <v>5.3449999999999998</v>
@@ -8122,7 +8125,7 @@
         <v>26</v>
       </c>
       <c r="B266" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C266">
         <v>5.0890000000000004</v>
@@ -8145,7 +8148,7 @@
         <v>26</v>
       </c>
       <c r="B267" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C267">
         <v>5.2969999999999997</v>
@@ -8168,7 +8171,7 @@
         <v>26</v>
       </c>
       <c r="B268" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C268">
         <v>5.2510000000000003</v>
@@ -8191,7 +8194,7 @@
         <v>26</v>
       </c>
       <c r="B269" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C269">
         <v>5.3170000000000002</v>
@@ -8214,7 +8217,7 @@
         <v>26</v>
       </c>
       <c r="B270" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C270">
         <v>5.3490000000000002</v>
@@ -8237,7 +8240,7 @@
         <v>26</v>
       </c>
       <c r="B271" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C271">
         <v>5.3630000000000004</v>
@@ -8260,7 +8263,7 @@
         <v>26</v>
       </c>
       <c r="B272" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C272">
         <v>5.1440000000000001</v>
@@ -8283,7 +8286,7 @@
         <v>26</v>
       </c>
       <c r="B273" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C273">
         <v>5.4240000000000004</v>
@@ -8306,7 +8309,7 @@
         <v>26</v>
       </c>
       <c r="B274" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C274">
         <v>5.2590000000000003</v>
@@ -8329,7 +8332,7 @@
         <v>26</v>
       </c>
       <c r="B275" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C275">
         <v>5.2560000000000002</v>
@@ -8352,7 +8355,7 @@
         <v>26</v>
       </c>
       <c r="B276" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C276">
         <v>5.4429999999999996</v>
@@ -8375,7 +8378,7 @@
         <v>26</v>
       </c>
       <c r="B277" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C277">
         <v>5.2990000000000004</v>
@@ -8398,7 +8401,7 @@
         <v>26</v>
       </c>
       <c r="B278" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C278">
         <v>5.4160000000000004</v>
@@ -8421,7 +8424,7 @@
         <v>26</v>
       </c>
       <c r="B279" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C279">
         <v>5.3680000000000003</v>
@@ -8444,7 +8447,7 @@
         <v>26</v>
       </c>
       <c r="B280" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C280">
         <v>5.343</v>
@@ -8467,7 +8470,7 @@
         <v>26</v>
       </c>
       <c r="B281" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C281">
         <v>5.484</v>
@@ -8490,7 +8493,7 @@
         <v>26</v>
       </c>
       <c r="B282" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C282">
         <v>5.282</v>
@@ -8513,7 +8516,7 @@
         <v>26</v>
       </c>
       <c r="B283" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C283">
         <v>5.4</v>
@@ -8536,7 +8539,7 @@
         <v>26</v>
       </c>
       <c r="B284" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C284">
         <v>5.42</v>
@@ -8559,7 +8562,7 @@
         <v>26</v>
       </c>
       <c r="B285" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C285">
         <v>5.35</v>
@@ -8582,7 +8585,7 @@
         <v>26</v>
       </c>
       <c r="B286" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C286">
         <v>5.4359999999999999</v>
@@ -8605,7 +8608,7 @@
         <v>26</v>
       </c>
       <c r="B287" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C287">
         <v>5.4720000000000004</v>
@@ -8628,7 +8631,7 @@
         <v>26</v>
       </c>
       <c r="B288" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C288">
         <v>5.0979999999999999</v>
@@ -8651,7 +8654,7 @@
         <v>26</v>
       </c>
       <c r="B289" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C289">
         <v>5.4130000000000003</v>
@@ -8674,7 +8677,7 @@
         <v>26</v>
       </c>
       <c r="B290" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C290">
         <v>5.4020000000000001</v>
@@ -8697,7 +8700,7 @@
         <v>26</v>
       </c>
       <c r="B291" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C291">
         <v>5.258</v>
@@ -8720,7 +8723,7 @@
         <v>26</v>
       </c>
       <c r="B292" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C292">
         <v>5.242</v>
@@ -8743,7 +8746,7 @@
         <v>26</v>
       </c>
       <c r="B293" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C293">
         <v>5.1429999999999998</v>
@@ -8766,7 +8769,7 @@
         <v>26</v>
       </c>
       <c r="B294" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C294">
         <v>5.0810000000000004</v>
@@ -8789,7 +8792,7 @@
         <v>26</v>
       </c>
       <c r="B295" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C295">
         <v>5.202</v>
@@ -8812,7 +8815,7 @@
         <v>26</v>
       </c>
       <c r="B296" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C296">
         <v>5.4050000000000002</v>
@@ -8835,7 +8838,7 @@
         <v>26</v>
       </c>
       <c r="B297" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C297">
         <v>5.17</v>
@@ -8858,7 +8861,7 @@
         <v>26</v>
       </c>
       <c r="B298" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C298">
         <v>5.03</v>
@@ -8881,7 +8884,7 @@
         <v>26</v>
       </c>
       <c r="B299" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C299">
         <v>5.3040000000000003</v>
@@ -8904,7 +8907,7 @@
         <v>26</v>
       </c>
       <c r="B300" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C300">
         <v>5.492</v>
@@ -8927,7 +8930,7 @@
         <v>26</v>
       </c>
       <c r="B301" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C301">
         <v>5.1849999999999996</v>
@@ -8973,7 +8976,7 @@
         <v>26</v>
       </c>
       <c r="B303" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C303">
         <v>5.0579999999999998</v>
@@ -8996,7 +8999,7 @@
         <v>26</v>
       </c>
       <c r="B304" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C304">
         <v>5.1109999999999998</v>
@@ -9042,7 +9045,7 @@
         <v>26</v>
       </c>
       <c r="B306" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C306">
         <v>5.3390000000000004</v>
@@ -9088,7 +9091,7 @@
         <v>26</v>
       </c>
       <c r="B308" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C308">
         <v>5.2140000000000004</v>
@@ -9111,7 +9114,7 @@
         <v>26</v>
       </c>
       <c r="B309" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C309">
         <v>5.3390000000000004</v>
@@ -9134,7 +9137,7 @@
         <v>26</v>
       </c>
       <c r="B310" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C310">
         <v>5.1829999999999998</v>
@@ -9180,7 +9183,7 @@
         <v>26</v>
       </c>
       <c r="B312" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C312">
         <v>5.4219999999999997</v>
@@ -9203,7 +9206,7 @@
         <v>26</v>
       </c>
       <c r="B313" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C313">
         <v>5.1210000000000004</v>
@@ -9226,7 +9229,7 @@
         <v>26</v>
       </c>
       <c r="B314" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C314">
         <v>5.173</v>
@@ -9249,7 +9252,7 @@
         <v>26</v>
       </c>
       <c r="B315" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C315">
         <v>5.173</v>
@@ -9272,7 +9275,7 @@
         <v>26</v>
       </c>
       <c r="B316" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C316">
         <v>5.1760000000000002</v>
@@ -9295,7 +9298,7 @@
         <v>26</v>
       </c>
       <c r="B317" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C317">
         <v>5.069</v>
@@ -9318,7 +9321,7 @@
         <v>26</v>
       </c>
       <c r="B318" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C318">
         <v>5.3070000000000004</v>
@@ -9341,7 +9344,7 @@
         <v>26</v>
       </c>
       <c r="B319" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C319">
         <v>5.3380000000000001</v>
@@ -9364,7 +9367,7 @@
         <v>26</v>
       </c>
       <c r="B320" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C320">
         <v>5.0419999999999998</v>
@@ -9387,7 +9390,7 @@
         <v>26</v>
       </c>
       <c r="B321" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C321">
         <v>5.4260000000000002</v>
@@ -9410,7 +9413,7 @@
         <v>26</v>
       </c>
       <c r="B322" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C322">
         <v>5.2919999999999998</v>
@@ -9433,7 +9436,7 @@
         <v>26</v>
       </c>
       <c r="B323" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C323">
         <v>5.2629999999999999</v>
@@ -9456,7 +9459,7 @@
         <v>26</v>
       </c>
       <c r="B324" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C324">
         <v>5.016</v>
@@ -9479,7 +9482,7 @@
         <v>26</v>
       </c>
       <c r="B325" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C325">
         <v>5.0919999999999996</v>
@@ -9502,7 +9505,7 @@
         <v>26</v>
       </c>
       <c r="B326" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C326">
         <v>5.2779999999999996</v>
@@ -9525,7 +9528,7 @@
         <v>26</v>
       </c>
       <c r="B327" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C327">
         <v>5.1459999999999999</v>
@@ -9548,7 +9551,7 @@
         <v>26</v>
       </c>
       <c r="B328" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C328">
         <v>5.3470000000000004</v>
@@ -9571,7 +9574,7 @@
         <v>26</v>
       </c>
       <c r="B329" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C329">
         <v>5.3390000000000004</v>
@@ -9594,7 +9597,7 @@
         <v>26</v>
       </c>
       <c r="B330" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C330">
         <v>5.3070000000000004</v>
@@ -9617,7 +9620,7 @@
         <v>26</v>
       </c>
       <c r="B331" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C331">
         <v>5.1109999999999998</v>
@@ -9640,7 +9643,7 @@
         <v>26</v>
       </c>
       <c r="B332" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C332">
         <v>5.4870000000000001</v>
@@ -9663,7 +9666,7 @@
         <v>26</v>
       </c>
       <c r="B333" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C333">
         <v>5.125</v>
@@ -9686,7 +9689,7 @@
         <v>26</v>
       </c>
       <c r="B334" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C334">
         <v>5.25</v>
@@ -9709,7 +9712,7 @@
         <v>26</v>
       </c>
       <c r="B335" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C335">
         <v>5.0599999999999996</v>
@@ -9732,7 +9735,7 @@
         <v>26</v>
       </c>
       <c r="B336" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C336">
         <v>5.0650000000000004</v>
@@ -9755,7 +9758,7 @@
         <v>26</v>
       </c>
       <c r="B337" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C337">
         <v>5.0990000000000002</v>
@@ -9778,7 +9781,7 @@
         <v>26</v>
       </c>
       <c r="B338" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C338">
         <v>5.4539999999999997</v>
@@ -9801,7 +9804,7 @@
         <v>26</v>
       </c>
       <c r="B339" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C339">
         <v>5.4279999999999999</v>
@@ -9824,7 +9827,7 @@
         <v>26</v>
       </c>
       <c r="B340" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C340">
         <v>5.13</v>
@@ -9847,7 +9850,7 @@
         <v>26</v>
       </c>
       <c r="B341" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C341">
         <v>5.32</v>
@@ -9870,7 +9873,7 @@
         <v>26</v>
       </c>
       <c r="B342" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C342">
         <v>5.15</v>
@@ -9893,7 +9896,7 @@
         <v>26</v>
       </c>
       <c r="B343" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C343">
         <v>5.3979999999999997</v>
@@ -9916,7 +9919,7 @@
         <v>26</v>
       </c>
       <c r="B344" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C344">
         <v>5.2919999999999998</v>
@@ -9939,7 +9942,7 @@
         <v>26</v>
       </c>
       <c r="B345" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C345">
         <v>5.2140000000000004</v>
@@ -9962,7 +9965,7 @@
         <v>26</v>
       </c>
       <c r="B346" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C346">
         <v>5.01</v>
@@ -9985,7 +9988,7 @@
         <v>26</v>
       </c>
       <c r="B347" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C347">
         <v>5.2510000000000003</v>
@@ -10008,7 +10011,7 @@
         <v>26</v>
       </c>
       <c r="B348" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C348">
         <v>5.306</v>
@@ -10031,7 +10034,7 @@
         <v>26</v>
       </c>
       <c r="B349" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C349">
         <v>5.4269999999999996</v>
@@ -10054,7 +10057,7 @@
         <v>26</v>
       </c>
       <c r="B350" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C350">
         <v>5.0469999999999997</v>
@@ -10077,7 +10080,7 @@
         <v>26</v>
       </c>
       <c r="B351" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C351">
         <v>5.226</v>
@@ -10100,7 +10103,7 @@
         <v>26</v>
       </c>
       <c r="B352" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C352">
         <v>5.0289999999999999</v>
@@ -10123,7 +10126,7 @@
         <v>26</v>
       </c>
       <c r="B353" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C353">
         <v>5.431</v>
@@ -10146,7 +10149,7 @@
         <v>26</v>
       </c>
       <c r="B354" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C354">
         <v>5.1340000000000003</v>
@@ -10169,7 +10172,7 @@
         <v>26</v>
       </c>
       <c r="B355" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C355">
         <v>5.34</v>
@@ -10192,7 +10195,7 @@
         <v>26</v>
       </c>
       <c r="B356" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C356">
         <v>5.3310000000000004</v>
@@ -10215,7 +10218,7 @@
         <v>26</v>
       </c>
       <c r="B357" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C357">
         <v>5.4960000000000004</v>
@@ -10238,7 +10241,7 @@
         <v>26</v>
       </c>
       <c r="B358" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C358">
         <v>5.18</v>
@@ -10284,7 +10287,7 @@
         <v>26</v>
       </c>
       <c r="B360" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C360">
         <v>5.2889999999999997</v>
@@ -10307,7 +10310,7 @@
         <v>26</v>
       </c>
       <c r="B361" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C361">
         <v>5.04</v>
@@ -10373,10 +10376,10 @@
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B364" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C364">
         <v>30.466999999999999</v>
@@ -10396,10 +10399,10 @@
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B365" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C365">
         <v>30.475000000000001</v>
@@ -10419,10 +10422,10 @@
     </row>
     <row r="366" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B366" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C366">
         <v>15.117000000000001</v>
@@ -10442,10 +10445,10 @@
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B367" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C367">
         <v>30.425999999999998</v>
@@ -10465,10 +10468,10 @@
     </row>
     <row r="368" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B368" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C368">
         <v>30.465</v>
@@ -10488,10 +10491,10 @@
     </row>
     <row r="369" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B369" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C369">
         <v>30.158999999999999</v>
@@ -10511,10 +10514,10 @@
     </row>
     <row r="370" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B370" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C370">
         <v>15.43</v>
@@ -10534,10 +10537,10 @@
     </row>
     <row r="371" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B371" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C371">
         <v>15.143000000000001</v>
@@ -10557,10 +10560,10 @@
     </row>
     <row r="372" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B372" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C372">
         <v>15.023</v>
@@ -10580,7 +10583,7 @@
     </row>
     <row r="373" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B373" t="s">
         <v>5</v>
@@ -10603,10 +10606,10 @@
     </row>
     <row r="374" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B374" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C374">
         <v>2.6659999999999999</v>
@@ -10626,10 +10629,10 @@
     </row>
     <row r="375" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B375" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C375">
         <v>2.7010000000000001</v>
@@ -10649,10 +10652,10 @@
     </row>
     <row r="376" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B376" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C376">
         <v>5.4379999999999997</v>
@@ -10672,10 +10675,10 @@
     </row>
     <row r="377" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B377" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C377">
         <v>5.3330000000000002</v>
@@ -10695,10 +10698,10 @@
     </row>
     <row r="378" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
+        <v>336</v>
+      </c>
+      <c r="B378" t="s">
         <v>337</v>
-      </c>
-      <c r="B378" t="s">
-        <v>338</v>
       </c>
       <c r="C378">
         <v>5.3170000000000002</v>
@@ -10718,10 +10721,10 @@
     </row>
     <row r="379" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B379" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C379">
         <v>5.194</v>
@@ -10741,10 +10744,10 @@
     </row>
     <row r="380" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B380" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C380">
         <v>5.4329999999999998</v>
@@ -10764,10 +10767,10 @@
     </row>
     <row r="381" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B381" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C381">
         <v>5.202</v>
@@ -10787,10 +10790,10 @@
     </row>
     <row r="382" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B382" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C382">
         <v>5.3010000000000002</v>
@@ -10810,7 +10813,7 @@
     </row>
     <row r="383" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B383" t="s">
         <v>12</v>
@@ -10834,10 +10837,10 @@
     </row>
     <row r="384" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B384" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C384">
         <v>50.493000000000002</v>
@@ -10858,10 +10861,10 @@
     </row>
     <row r="385" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B385" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C385">
         <v>50.533000000000001</v>
@@ -10882,10 +10885,10 @@
     </row>
     <row r="386" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B386" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C386">
         <v>50.744999999999997</v>
@@ -10906,10 +10909,10 @@
     </row>
     <row r="387" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B387" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C387">
         <v>50.841999999999999</v>
@@ -10930,10 +10933,10 @@
     </row>
     <row r="388" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B388" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C388">
         <v>50.472000000000001</v>
@@ -10953,10 +10956,10 @@
     </row>
     <row r="389" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B389" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C389">
         <v>50.191000000000003</v>
@@ -10976,10 +10979,10 @@
     </row>
     <row r="390" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B390" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C390">
         <v>50.548000000000002</v>
@@ -10999,10 +11002,10 @@
     </row>
     <row r="391" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B391" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C391">
         <v>50.378</v>
@@ -11022,10 +11025,10 @@
     </row>
     <row r="392" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B392" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C392">
         <v>50.152999999999999</v>
@@ -11045,10 +11048,10 @@
     </row>
     <row r="393" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B393" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C393">
         <v>50.963000000000001</v>
@@ -11068,10 +11071,10 @@
     </row>
     <row r="394" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B394" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C394">
         <v>50.683</v>
@@ -11091,10 +11094,10 @@
     </row>
     <row r="395" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B395" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C395">
         <v>50.287999999999997</v>
@@ -11114,10 +11117,10 @@
     </row>
     <row r="396" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B396" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C396">
         <v>50.051000000000002</v>
@@ -11137,10 +11140,10 @@
     </row>
     <row r="397" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B397" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C397">
         <v>50.884999999999998</v>
@@ -11160,10 +11163,10 @@
     </row>
     <row r="398" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B398" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C398">
         <v>50.530999999999999</v>
@@ -11183,10 +11186,10 @@
     </row>
     <row r="399" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B399" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C399">
         <v>50.776000000000003</v>
@@ -11206,10 +11209,10 @@
     </row>
     <row r="400" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B400" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C400">
         <v>50.625999999999998</v>
@@ -11229,10 +11232,10 @@
     </row>
     <row r="401" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B401" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C401">
         <v>50.295000000000002</v>
@@ -11252,10 +11255,10 @@
     </row>
     <row r="402" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B402" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C402">
         <v>50.91</v>
@@ -11275,10 +11278,10 @@
     </row>
     <row r="403" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B403" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C403">
         <v>50.061999999999998</v>
@@ -11298,10 +11301,10 @@
     </row>
     <row r="404" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B404" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C404">
         <v>50.579000000000001</v>
@@ -11321,10 +11324,10 @@
     </row>
     <row r="405" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B405" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C405">
         <v>50.859000000000002</v>
@@ -11344,10 +11347,10 @@
     </row>
     <row r="406" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B406" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C406">
         <v>50.847999999999999</v>
@@ -11367,10 +11370,10 @@
     </row>
     <row r="407" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B407" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C407">
         <v>50.969000000000001</v>
@@ -11390,10 +11393,10 @@
     </row>
     <row r="408" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B408" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C408">
         <v>50.264000000000003</v>
@@ -11413,10 +11416,10 @@
     </row>
     <row r="409" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B409" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C409">
         <v>10.818</v>
@@ -11436,10 +11439,10 @@
     </row>
     <row r="410" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B410" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C410">
         <v>5.9450000000000003</v>
@@ -11459,10 +11462,10 @@
     </row>
     <row r="411" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B411" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C411">
         <v>5.2140000000000004</v>
@@ -11482,10 +11485,10 @@
     </row>
     <row r="412" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B412" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C412">
         <v>10.419</v>
@@ -11505,10 +11508,10 @@
     </row>
     <row r="413" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B413" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C413">
         <v>5.9640000000000004</v>
@@ -11528,10 +11531,10 @@
     </row>
     <row r="414" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B414" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C414">
         <v>5.4020000000000001</v>
@@ -11551,10 +11554,10 @@
     </row>
     <row r="415" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B415" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C415">
         <v>5.3250000000000002</v>
@@ -11574,10 +11577,10 @@
     </row>
     <row r="416" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B416" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C416">
         <v>5.3630000000000004</v>
@@ -11597,10 +11600,10 @@
     </row>
     <row r="417" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B417" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C417">
         <v>5.7530000000000001</v>
@@ -11620,10 +11623,10 @@
     </row>
     <row r="418" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B418" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C418">
         <v>5.609</v>
@@ -11643,10 +11646,10 @@
     </row>
     <row r="419" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B419" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C419">
         <v>50.308999999999997</v>
@@ -11666,10 +11669,10 @@
     </row>
     <row r="420" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
+        <v>394</v>
+      </c>
+      <c r="B420" t="s">
         <v>395</v>
-      </c>
-      <c r="B420" t="s">
-        <v>396</v>
       </c>
       <c r="C420">
         <v>50.152000000000001</v>
@@ -11689,10 +11692,10 @@
     </row>
     <row r="421" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B421" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C421">
         <v>1.7789999999999999</v>
@@ -11712,10 +11715,10 @@
     </row>
     <row r="422" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B422" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C422">
         <v>5.3550000000000004</v>
@@ -11735,10 +11738,10 @@
     </row>
     <row r="423" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B423" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C423">
         <v>5.3639999999999999</v>
@@ -11758,10 +11761,10 @@
     </row>
     <row r="424" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B424" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C424">
         <v>5.4329999999999998</v>
@@ -11781,10 +11784,10 @@
     </row>
     <row r="425" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B425" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C425">
         <v>5.4770000000000003</v>
@@ -11804,10 +11807,10 @@
     </row>
     <row r="426" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B426" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C426">
         <v>5.3730000000000002</v>
@@ -11827,10 +11830,10 @@
     </row>
     <row r="427" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B427" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C427">
         <v>5.4459999999999997</v>
@@ -11850,10 +11853,10 @@
     </row>
     <row r="428" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B428" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C428">
         <v>5.1609999999999996</v>
@@ -11873,10 +11876,10 @@
     </row>
     <row r="429" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B429" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C429">
         <v>5.5</v>
@@ -11896,10 +11899,10 @@
     </row>
     <row r="430" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B430" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C430">
         <v>50.546999999999997</v>
@@ -11919,10 +11922,10 @@
     </row>
     <row r="431" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B431" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C431">
         <v>50.677999999999997</v>
@@ -11942,10 +11945,10 @@
     </row>
     <row r="432" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B432" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C432">
         <v>50.12</v>
@@ -11965,10 +11968,10 @@
     </row>
     <row r="433" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B433" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C433">
         <v>50.034999999999997</v>
@@ -11988,10 +11991,10 @@
     </row>
     <row r="434" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B434" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C434">
         <v>50.933999999999997</v>
@@ -12011,10 +12014,10 @@
     </row>
     <row r="435" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B435" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C435">
         <v>50.628</v>
@@ -12034,10 +12037,10 @@
     </row>
     <row r="436" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B436" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C436">
         <v>50.253999999999998</v>
@@ -12057,10 +12060,10 @@
     </row>
     <row r="437" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B437" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C437">
         <v>50.506</v>
@@ -12080,10 +12083,10 @@
     </row>
     <row r="438" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B438" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C438">
         <v>50.405000000000001</v>
@@ -12103,10 +12106,10 @@
     </row>
     <row r="439" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B439" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C439">
         <v>50.289000000000001</v>
@@ -12126,10 +12129,10 @@
     </row>
     <row r="440" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B440" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C440">
         <v>5.4370000000000003</v>
@@ -12149,10 +12152,10 @@
     </row>
     <row r="441" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B441" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C441">
         <v>5.1390000000000002</v>
@@ -12172,10 +12175,10 @@
     </row>
     <row r="442" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B442" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C442">
         <v>5.0540000000000003</v>
@@ -12195,10 +12198,10 @@
     </row>
     <row r="443" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B443" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C443">
         <v>5.3860000000000001</v>
@@ -12218,10 +12221,10 @@
     </row>
     <row r="444" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B444" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C444">
         <v>5.2539999999999996</v>
@@ -12241,10 +12244,10 @@
     </row>
     <row r="445" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B445" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C445">
         <v>5.085</v>
@@ -12264,10 +12267,10 @@
     </row>
     <row r="446" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B446" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C446">
         <v>5.4850000000000003</v>
@@ -12287,10 +12290,10 @@
     </row>
     <row r="447" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B447" t="s">
-        <v>423</v>
+        <v>530</v>
       </c>
       <c r="C447">
         <v>5.46</v>
@@ -12310,19 +12313,19 @@
     </row>
     <row r="448" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B448" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C448">
-        <v>50.378</v>
+        <v>5.218</v>
       </c>
       <c r="D448">
-        <v>0.30206714782544081</v>
+        <v>1.9156796289994844</v>
       </c>
       <c r="E448">
-        <v>311.86150285613746</v>
+        <v>-14.829843582703578</v>
       </c>
       <c r="F448" s="1" t="s">
         <v>22</v>
@@ -12333,19 +12336,19 @@
     </row>
     <row r="449" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B449" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C449">
-        <v>50.796999999999997</v>
+        <v>50.378</v>
       </c>
       <c r="D449">
-        <v>9.3430792535467669E-2</v>
+        <v>0.30206714782544081</v>
       </c>
       <c r="E449">
-        <v>-1.0695776380307294</v>
+        <v>311.86150285613746</v>
       </c>
       <c r="F449" s="1" t="s">
         <v>22</v>
@@ -12356,19 +12359,19 @@
     </row>
     <row r="450" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B450" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C450">
-        <v>50.671999999999997</v>
+        <v>50.796999999999997</v>
       </c>
       <c r="D450">
-        <v>0.10297085040690732</v>
+        <v>9.3430792535467669E-2</v>
       </c>
       <c r="E450">
-        <v>3.6520261512441614</v>
+        <v>-1.0695776380307294</v>
       </c>
       <c r="F450" s="1" t="s">
         <v>22</v>
@@ -12379,19 +12382,19 @@
     </row>
     <row r="451" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B451" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C451">
-        <v>50.725999999999999</v>
+        <v>50.671999999999997</v>
       </c>
       <c r="D451">
-        <v>0.10640686837124452</v>
+        <v>0.10297085040690732</v>
       </c>
       <c r="E451">
-        <v>4.527245405172355</v>
+        <v>3.6520261512441614</v>
       </c>
       <c r="F451" s="1" t="s">
         <v>22</v>
@@ -12402,19 +12405,19 @@
     </row>
     <row r="452" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B452" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C452">
-        <v>50.335000000000001</v>
+        <v>50.725999999999999</v>
       </c>
       <c r="D452">
-        <v>0.11051232406738244</v>
+        <v>0.10640686837124452</v>
       </c>
       <c r="E452">
-        <v>0.76078550259576971</v>
+        <v>4.527245405172355</v>
       </c>
       <c r="F452" s="1" t="s">
         <v>22</v>
@@ -12425,19 +12428,19 @@
     </row>
     <row r="453" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B453" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C453">
-        <v>50.213999999999999</v>
+        <v>50.335000000000001</v>
       </c>
       <c r="D453">
-        <v>0.12120901487772387</v>
+        <v>0.11051232406738244</v>
       </c>
       <c r="E453">
-        <v>0.65497474393376365</v>
+        <v>0.76078550259576971</v>
       </c>
       <c r="F453" s="1" t="s">
         <v>22</v>
@@ -12448,19 +12451,19 @@
     </row>
     <row r="454" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B454" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C454">
-        <v>50.546999999999997</v>
+        <v>50.213999999999999</v>
       </c>
       <c r="D454">
-        <v>0.10072639773198586</v>
+        <v>0.12120901487772387</v>
       </c>
       <c r="E454">
-        <v>-3.9644353088330604</v>
+        <v>0.65497474393376365</v>
       </c>
       <c r="F454" s="1" t="s">
         <v>22</v>
@@ -12471,19 +12474,19 @@
     </row>
     <row r="455" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B455" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C455">
-        <v>50.125</v>
+        <v>50.546999999999997</v>
       </c>
       <c r="D455">
-        <v>0.11059994616043137</v>
+        <v>0.10072639773198586</v>
       </c>
       <c r="E455">
-        <v>-3.2526867276578351</v>
+        <v>-3.9644353088330604</v>
       </c>
       <c r="F455" s="1" t="s">
         <v>22</v>
@@ -12494,19 +12497,19 @@
     </row>
     <row r="456" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B456" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C456">
-        <v>50.052</v>
+        <v>50.125</v>
       </c>
       <c r="D456">
-        <v>0.13636107250752352</v>
+        <v>0.11059994616043137</v>
       </c>
       <c r="E456">
-        <v>-4.7281907983513811</v>
+        <v>-3.2526867276578351</v>
       </c>
       <c r="F456" s="1" t="s">
         <v>22</v>
@@ -12517,19 +12520,19 @@
     </row>
     <row r="457" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B457" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C457">
-        <v>50.067</v>
+        <v>50.052</v>
       </c>
       <c r="D457">
-        <v>0.12468073706089763</v>
+        <v>0.13636107250752352</v>
       </c>
       <c r="E457">
-        <v>-0.33717703461865156</v>
+        <v>-4.7281907983513811</v>
       </c>
       <c r="F457" s="1" t="s">
         <v>22</v>
@@ -12540,19 +12543,19 @@
     </row>
     <row r="458" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B458" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C458">
-        <v>5.4740000000000002</v>
+        <v>50.067</v>
       </c>
       <c r="D458">
-        <v>6.2008088953811775</v>
+        <v>0.12468073706089763</v>
       </c>
       <c r="E458">
-        <v>71.364264101633992</v>
+        <v>-0.33717703461865156</v>
       </c>
       <c r="F458" s="1" t="s">
         <v>22</v>
@@ -12563,19 +12566,19 @@
     </row>
     <row r="459" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B459" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C459">
-        <v>5.431</v>
+        <v>5.4740000000000002</v>
       </c>
       <c r="D459">
-        <v>3.1954048051618265</v>
+        <v>6.2008088953811775</v>
       </c>
       <c r="E459">
-        <v>-13.410149095115646</v>
+        <v>71.364264101633992</v>
       </c>
       <c r="F459" s="1" t="s">
         <v>22</v>
@@ -12586,19 +12589,19 @@
     </row>
     <row r="460" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B460" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C460">
-        <v>5.008</v>
+        <v>5.431</v>
       </c>
       <c r="D460">
-        <v>6.3586115881071716</v>
+        <v>3.1954048051618265</v>
       </c>
       <c r="E460">
-        <v>60.488885930226658</v>
+        <v>-13.410149095115646</v>
       </c>
       <c r="F460" s="1" t="s">
         <v>22</v>
@@ -12609,19 +12612,19 @@
     </row>
     <row r="461" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B461" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C461">
-        <v>5.1829999999999998</v>
+        <v>5.008</v>
       </c>
       <c r="D461">
-        <v>7.0261732394862344</v>
+        <v>6.3586115881071716</v>
       </c>
       <c r="E461">
-        <v>23.09553813030065</v>
+        <v>60.488885930226658</v>
       </c>
       <c r="F461" s="1" t="s">
         <v>22</v>
@@ -12632,19 +12635,19 @@
     </row>
     <row r="462" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B462" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C462">
-        <v>5.3959999999999999</v>
+        <v>5.1829999999999998</v>
       </c>
       <c r="D462">
-        <v>6.1537961945454436</v>
+        <v>7.0261732394862344</v>
       </c>
       <c r="E462">
-        <v>-3.1699623769167538</v>
+        <v>23.09553813030065</v>
       </c>
       <c r="F462" s="1" t="s">
         <v>22</v>
@@ -12655,19 +12658,19 @@
     </row>
     <row r="463" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B463" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C463">
-        <v>2.198</v>
+        <v>5.3959999999999999</v>
       </c>
       <c r="D463">
-        <v>7.1951450520659845</v>
+        <v>6.1537961945454436</v>
       </c>
       <c r="E463">
-        <v>-6.2135688409490761</v>
+        <v>-3.1699623769167538</v>
       </c>
       <c r="F463" s="1" t="s">
         <v>22</v>
@@ -12678,19 +12681,19 @@
     </row>
     <row r="464" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B464" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C464">
-        <v>2.0979999999999999</v>
+        <v>2.198</v>
       </c>
       <c r="D464">
-        <v>8.3486118198838781</v>
+        <v>7.1951450520659845</v>
       </c>
       <c r="E464">
-        <v>-9.0042047860630738</v>
+        <v>-6.2135688409490761</v>
       </c>
       <c r="F464" s="1" t="s">
         <v>22</v>
@@ -12701,19 +12704,19 @@
     </row>
     <row r="465" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B465" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C465">
-        <v>2.0470000000000002</v>
+        <v>2.0979999999999999</v>
       </c>
       <c r="D465">
-        <v>8.6041181986914754</v>
+        <v>8.3486118198838781</v>
       </c>
       <c r="E465">
-        <v>-11.232857347224755</v>
+        <v>-9.0042047860630738</v>
       </c>
       <c r="F465" s="1" t="s">
         <v>22</v>
@@ -12724,19 +12727,19 @@
     </row>
     <row r="466" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B466" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C466">
-        <v>2.4540000000000002</v>
+        <v>2.0470000000000002</v>
       </c>
       <c r="D466">
-        <v>5.2091557458821933</v>
+        <v>8.6041181986914754</v>
       </c>
       <c r="E466">
-        <v>-13.048976791826494</v>
+        <v>-11.232857347224755</v>
       </c>
       <c r="F466" s="1" t="s">
         <v>22</v>
@@ -12747,19 +12750,19 @@
     </row>
     <row r="467" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B467" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C467">
-        <v>5.3230000000000004</v>
+        <v>2.4540000000000002</v>
       </c>
       <c r="D467">
-        <v>3.4161309624072227</v>
+        <v>5.2091557458821933</v>
       </c>
       <c r="E467">
-        <v>-12.575885386810222</v>
+        <v>-13.048976791826494</v>
       </c>
       <c r="F467" s="1" t="s">
         <v>22</v>
@@ -12770,19 +12773,19 @@
     </row>
     <row r="468" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B468" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C468">
-        <v>16.173999999999999</v>
+        <v>5.3230000000000004</v>
       </c>
       <c r="D468">
-        <v>1.2070917829116696</v>
+        <v>3.4161309624072227</v>
       </c>
       <c r="E468">
-        <v>385.25412886357367</v>
+        <v>-12.575885386810222</v>
       </c>
       <c r="F468" s="1" t="s">
         <v>22</v>
@@ -12793,19 +12796,19 @@
     </row>
     <row r="469" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B469" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C469">
-        <v>51</v>
+        <v>16.173999999999999</v>
       </c>
       <c r="D469">
-        <v>0.13838452825619324</v>
+        <v>1.2070917829116696</v>
       </c>
       <c r="E469">
-        <v>5.9456230393615108</v>
+        <v>385.25412886357367</v>
       </c>
       <c r="F469" s="1" t="s">
         <v>22</v>
@@ -12816,19 +12819,19 @@
     </row>
     <row r="470" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B470" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C470">
-        <v>50.603000000000002</v>
+        <v>51</v>
       </c>
       <c r="D470">
-        <v>0.16792970842768851</v>
+        <v>0.13838452825619324</v>
       </c>
       <c r="E470">
-        <v>32.071650021184652</v>
+        <v>5.9456230393615108</v>
       </c>
       <c r="F470" s="1" t="s">
         <v>22</v>
@@ -12839,19 +12842,19 @@
     </row>
     <row r="471" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B471" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C471">
-        <v>50.401000000000003</v>
+        <v>50.603000000000002</v>
       </c>
       <c r="D471">
-        <v>0.15274141559766216</v>
+        <v>0.16792970842768851</v>
       </c>
       <c r="E471">
-        <v>6.479248286556146</v>
+        <v>32.071650021184652</v>
       </c>
       <c r="F471" s="1" t="s">
         <v>22</v>
@@ -12862,19 +12865,19 @@
     </row>
     <row r="472" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B472" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C472">
-        <v>50.209000000000003</v>
+        <v>50.401000000000003</v>
       </c>
       <c r="D472">
-        <v>0.14502733184136876</v>
+        <v>0.15274141559766216</v>
       </c>
       <c r="E472">
-        <v>5.6208838317800023</v>
+        <v>6.479248286556146</v>
       </c>
       <c r="F472" s="1" t="s">
         <v>22</v>
@@ -12885,19 +12888,19 @@
     </row>
     <row r="473" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B473" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C473">
-        <v>50.387999999999998</v>
+        <v>50.209000000000003</v>
       </c>
       <c r="D473">
-        <v>0.11013466689916772</v>
+        <v>0.14502733184136876</v>
       </c>
       <c r="E473">
-        <v>4.5738060494049009</v>
+        <v>5.6208838317800023</v>
       </c>
       <c r="F473" s="1" t="s">
         <v>22</v>
@@ -12908,19 +12911,19 @@
     </row>
     <row r="474" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B474" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C474">
-        <v>50.622</v>
+        <v>50.387999999999998</v>
       </c>
       <c r="D474">
-        <v>0.13545451401803535</v>
+        <v>0.11013466689916772</v>
       </c>
       <c r="E474">
-        <v>5.1150544729860776</v>
+        <v>4.5738060494049009</v>
       </c>
       <c r="F474" s="1" t="s">
         <v>22</v>
@@ -12931,19 +12934,19 @@
     </row>
     <row r="475" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B475" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C475">
-        <v>50.414999999999999</v>
+        <v>50.622</v>
       </c>
       <c r="D475">
-        <v>9.161556586908462E-2</v>
+        <v>0.13545451401803535</v>
       </c>
       <c r="E475">
-        <v>3.8565921490667385</v>
+        <v>5.1150544729860776</v>
       </c>
       <c r="F475" s="1" t="s">
         <v>22</v>
@@ -12954,19 +12957,19 @@
     </row>
     <row r="476" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B476" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C476">
-        <v>50.031999999999996</v>
+        <v>50.414999999999999</v>
       </c>
       <c r="D476">
-        <v>9.7556348788434014E-2</v>
+        <v>9.161556586908462E-2</v>
       </c>
       <c r="E476">
-        <v>5.7099026741759751</v>
+        <v>3.8565921490667385</v>
       </c>
       <c r="F476" s="1" t="s">
         <v>22</v>
@@ -12977,19 +12980,19 @@
     </row>
     <row r="477" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B477" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C477">
-        <v>50.536999999999999</v>
+        <v>50.031999999999996</v>
       </c>
       <c r="D477">
-        <v>0.10903333848601943</v>
+        <v>9.7556348788434014E-2</v>
       </c>
       <c r="E477">
-        <v>7.5202654609738673</v>
+        <v>5.7099026741759751</v>
       </c>
       <c r="F477" s="1" t="s">
         <v>22</v>
@@ -13000,19 +13003,19 @@
     </row>
     <row r="478" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B478" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C478">
-        <v>21.593</v>
+        <v>50.536999999999999</v>
       </c>
       <c r="D478">
-        <v>0.95814537243707443</v>
+        <v>0.10903333848601943</v>
       </c>
       <c r="E478">
-        <v>416.23962862476782</v>
+        <v>7.5202654609738673</v>
       </c>
       <c r="F478" s="1" t="s">
         <v>22</v>
@@ -13023,19 +13026,19 @@
     </row>
     <row r="479" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B479" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C479">
-        <v>50.308999999999997</v>
+        <v>21.593</v>
       </c>
       <c r="D479">
-        <v>0.1682759026515834</v>
+        <v>0.95814537243707443</v>
       </c>
       <c r="E479">
-        <v>9.7214169333218372</v>
+        <v>416.23962862476782</v>
       </c>
       <c r="F479" s="1" t="s">
         <v>22</v>
@@ -13046,19 +13049,19 @@
     </row>
     <row r="480" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B480" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C480">
-        <v>50.216999999999999</v>
+        <v>50.308999999999997</v>
       </c>
       <c r="D480">
-        <v>0.2442578546744891</v>
+        <v>0.1682759026515834</v>
       </c>
       <c r="E480">
-        <v>4.2925082752137165</v>
+        <v>9.7214169333218372</v>
       </c>
       <c r="F480" s="1" t="s">
         <v>22</v>
@@ -13069,19 +13072,19 @@
     </row>
     <row r="481" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B481" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C481">
-        <v>50.892000000000003</v>
+        <v>50.216999999999999</v>
       </c>
       <c r="D481">
-        <v>0.19922834980309365</v>
+        <v>0.2442578546744891</v>
       </c>
       <c r="E481">
-        <v>1.8789585040534931</v>
+        <v>4.2925082752137165</v>
       </c>
       <c r="F481" s="1" t="s">
         <v>22</v>
@@ -13092,19 +13095,19 @@
     </row>
     <row r="482" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B482" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C482">
-        <v>50.131</v>
+        <v>50.892000000000003</v>
       </c>
       <c r="D482">
-        <v>0.1407032838424345</v>
+        <v>0.19922834980309365</v>
       </c>
       <c r="E482">
-        <v>1.2972920850549841</v>
+        <v>1.8789585040534931</v>
       </c>
       <c r="F482" s="1" t="s">
         <v>22</v>
@@ -13115,19 +13118,19 @@
     </row>
     <row r="483" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B483" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C483">
-        <v>50.177</v>
+        <v>50.131</v>
       </c>
       <c r="D483">
-        <v>0.14003498358979771</v>
+        <v>0.1407032838424345</v>
       </c>
       <c r="E483">
-        <v>0.56576208739342704</v>
+        <v>1.2972920850549841</v>
       </c>
       <c r="F483" s="1" t="s">
         <v>22</v>
@@ -13138,19 +13141,19 @@
     </row>
     <row r="484" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B484" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C484">
-        <v>50.914999999999999</v>
+        <v>50.177</v>
       </c>
       <c r="D484">
-        <v>0.14590262340512242</v>
+        <v>0.14003498358979771</v>
       </c>
       <c r="E484">
-        <v>1.4814830258907712</v>
+        <v>0.56576208739342704</v>
       </c>
       <c r="F484" s="1" t="s">
         <v>22</v>
@@ -13161,19 +13164,19 @@
     </row>
     <row r="485" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B485" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C485">
-        <v>50.256999999999998</v>
+        <v>50.914999999999999</v>
       </c>
       <c r="D485">
-        <v>0.13835229124761694</v>
+        <v>0.14590262340512242</v>
       </c>
       <c r="E485">
-        <v>2.4831032978517982</v>
+        <v>1.4814830258907712</v>
       </c>
       <c r="F485" s="1" t="s">
         <v>22</v>
@@ -13184,19 +13187,19 @@
     </row>
     <row r="486" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B486" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C486">
-        <v>50.534999999999997</v>
+        <v>50.256999999999998</v>
       </c>
       <c r="D486">
-        <v>0.15580416782799472</v>
+        <v>0.13835229124761694</v>
       </c>
       <c r="E486">
-        <v>1.7954895662449708</v>
+        <v>2.4831032978517982</v>
       </c>
       <c r="F486" s="1" t="s">
         <v>22</v>
@@ -13207,19 +13210,19 @@
     </row>
     <row r="487" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B487" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C487">
-        <v>50.695999999999998</v>
+        <v>50.534999999999997</v>
       </c>
       <c r="D487">
-        <v>0.15934382609624223</v>
+        <v>0.15580416782799472</v>
       </c>
       <c r="E487">
-        <v>5.5973275605985471</v>
+        <v>1.7954895662449708</v>
       </c>
       <c r="F487" s="1" t="s">
         <v>22</v>
@@ -13230,19 +13233,19 @@
     </row>
     <row r="488" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B488" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C488">
-        <v>23.402000000000001</v>
+        <v>50.695999999999998</v>
       </c>
       <c r="D488">
-        <v>0.85748516942928654</v>
+        <v>0.15934382609624223</v>
       </c>
       <c r="E488">
-        <v>467.00811869816977</v>
+        <v>5.5973275605985471</v>
       </c>
       <c r="F488" s="1" t="s">
         <v>22</v>
@@ -13253,19 +13256,19 @@
     </row>
     <row r="489" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B489" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C489">
-        <v>50.578000000000003</v>
+        <v>23.402000000000001</v>
       </c>
       <c r="D489">
-        <v>0.11977925354393876</v>
+        <v>0.85748516942928654</v>
       </c>
       <c r="E489">
-        <v>8.1306642277568848</v>
+        <v>467.00811869816977</v>
       </c>
       <c r="F489" s="1" t="s">
         <v>22</v>
@@ -13276,19 +13279,19 @@
     </row>
     <row r="490" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B490" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C490">
-        <v>50.119</v>
+        <v>50.578000000000003</v>
       </c>
       <c r="D490">
-        <v>0.16594228589171156</v>
+        <v>0.11977925354393876</v>
       </c>
       <c r="E490">
-        <v>24.842446332432683</v>
+        <v>8.1306642277568848</v>
       </c>
       <c r="F490" s="1" t="s">
         <v>22</v>
@@ -13299,19 +13302,19 @@
     </row>
     <row r="491" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B491" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C491">
-        <v>50.012</v>
+        <v>50.119</v>
       </c>
       <c r="D491">
-        <v>0.14765963414603078</v>
+        <v>0.16594228589171156</v>
       </c>
       <c r="E491">
-        <v>4.2168890233419276</v>
+        <v>24.842446332432683</v>
       </c>
       <c r="F491" s="1" t="s">
         <v>22</v>
@@ -13322,19 +13325,19 @@
     </row>
     <row r="492" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B492" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C492">
-        <v>50.802999999999997</v>
+        <v>50.012</v>
       </c>
       <c r="D492">
-        <v>8.9511572281332524E-2</v>
+        <v>0.14765963414603078</v>
       </c>
       <c r="E492">
-        <v>3.6353945623549464</v>
+        <v>4.2168890233419276</v>
       </c>
       <c r="F492" s="1" t="s">
         <v>22</v>
@@ -13345,19 +13348,19 @@
     </row>
     <row r="493" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B493" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C493">
-        <v>50.728000000000002</v>
+        <v>50.802999999999997</v>
       </c>
       <c r="D493">
-        <v>8.4986574746777274E-2</v>
+        <v>8.9511572281332524E-2</v>
       </c>
       <c r="E493">
-        <v>1.6121052837611707</v>
+        <v>3.6353945623549464</v>
       </c>
       <c r="F493" s="1" t="s">
         <v>22</v>
@@ -13368,19 +13371,19 @@
     </row>
     <row r="494" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B494" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C494">
-        <v>50.619</v>
+        <v>50.728000000000002</v>
       </c>
       <c r="D494">
-        <v>8.6164436489493568E-2</v>
+        <v>8.4986574746777274E-2</v>
       </c>
       <c r="E494">
-        <v>4.4534293511980145</v>
+        <v>1.6121052837611707</v>
       </c>
       <c r="F494" s="1" t="s">
         <v>22</v>
@@ -13391,19 +13394,19 @@
     </row>
     <row r="495" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B495" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C495">
-        <v>50.972999999999999</v>
+        <v>50.619</v>
       </c>
       <c r="D495">
-        <v>7.6527668625873554E-2</v>
+        <v>8.6164436489493568E-2</v>
       </c>
       <c r="E495">
-        <v>5.3438125342408895</v>
+        <v>4.4534293511980145</v>
       </c>
       <c r="F495" s="1" t="s">
         <v>22</v>
@@ -13414,19 +13417,19 @@
     </row>
     <row r="496" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B496" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C496">
-        <v>50.637999999999998</v>
+        <v>50.972999999999999</v>
       </c>
       <c r="D496">
-        <v>8.4745281545207565E-2</v>
+        <v>7.6527668625873554E-2</v>
       </c>
       <c r="E496">
-        <v>5.47990695781602</v>
+        <v>5.3438125342408895</v>
       </c>
       <c r="F496" s="1" t="s">
         <v>22</v>
@@ -13437,19 +13440,19 @@
     </row>
     <row r="497" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B497" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C497">
-        <v>50.688000000000002</v>
+        <v>50.637999999999998</v>
       </c>
       <c r="D497">
-        <v>0.10888073731331184</v>
+        <v>8.4745281545207565E-2</v>
       </c>
       <c r="E497">
-        <v>5.4856492034445061</v>
+        <v>5.47990695781602</v>
       </c>
       <c r="F497" s="1" t="s">
         <v>22</v>
@@ -13460,19 +13463,19 @@
     </row>
     <row r="498" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B498" t="s">
-        <v>342</v>
+        <v>472</v>
       </c>
       <c r="C498">
-        <v>5.2969999999999997</v>
+        <v>50.688000000000002</v>
       </c>
       <c r="D498">
-        <v>7.0922367923013496</v>
+        <v>0.10888073731331184</v>
       </c>
       <c r="E498">
-        <v>116.00144001288373</v>
+        <v>5.4856492034445061</v>
       </c>
       <c r="F498" s="1" t="s">
         <v>22</v>
@@ -13483,19 +13486,19 @@
     </row>
     <row r="499" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B499" t="s">
-        <v>474</v>
+        <v>341</v>
       </c>
       <c r="C499">
-        <v>5.3490000000000002</v>
+        <v>5.2969999999999997</v>
       </c>
       <c r="D499">
-        <v>3.9635782151055703</v>
+        <v>7.0922367923013496</v>
       </c>
       <c r="E499">
-        <v>4.5251001313251926</v>
+        <v>116.00144001288373</v>
       </c>
       <c r="F499" s="1" t="s">
         <v>22</v>
@@ -13506,19 +13509,19 @@
     </row>
     <row r="500" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B500" t="s">
-        <v>364</v>
+        <v>473</v>
       </c>
       <c r="C500">
-        <v>5.157</v>
+        <v>5.3490000000000002</v>
       </c>
       <c r="D500">
-        <v>6.6363634243535765</v>
+        <v>3.9635782151055703</v>
       </c>
       <c r="E500">
-        <v>-8.9343706690609928</v>
+        <v>4.5251001313251926</v>
       </c>
       <c r="F500" s="1" t="s">
         <v>22</v>
@@ -13529,19 +13532,19 @@
     </row>
     <row r="501" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A501" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B501" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C501">
-        <v>3.4350000000000001</v>
+        <v>5.157</v>
       </c>
       <c r="D501">
-        <v>5.2219187620511871</v>
+        <v>6.6363634243535765</v>
       </c>
       <c r="E501">
-        <v>-7.1292615618814814</v>
+        <v>-8.9343706690609928</v>
       </c>
       <c r="F501" s="1" t="s">
         <v>22</v>
@@ -13552,19 +13555,19 @@
     </row>
     <row r="502" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A502" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B502" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C502">
-        <v>3.6869999999999998</v>
+        <v>3.4350000000000001</v>
       </c>
       <c r="D502">
-        <v>4.2231034170135295</v>
+        <v>5.2219187620511871</v>
       </c>
       <c r="E502">
-        <v>-6.9376699820050085</v>
+        <v>-7.1292615618814814</v>
       </c>
       <c r="F502" s="1" t="s">
         <v>22</v>
@@ -13575,19 +13578,19 @@
     </row>
     <row r="503" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A503" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B503" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C503">
-        <v>4.5810000000000004</v>
+        <v>3.6869999999999998</v>
       </c>
       <c r="D503">
-        <v>4.7572980871983761</v>
+        <v>4.2231034170135295</v>
       </c>
       <c r="E503">
-        <v>-12.673010588959787</v>
+        <v>-6.9376699820050085</v>
       </c>
       <c r="F503" s="1" t="s">
         <v>22</v>
@@ -13598,19 +13601,19 @@
     </row>
     <row r="504" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B504" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C504">
-        <v>6.0419999999999998</v>
+        <v>4.5810000000000004</v>
       </c>
       <c r="D504">
-        <v>5.1105379415961201</v>
+        <v>4.7572980871983761</v>
       </c>
       <c r="E504">
-        <v>-14.91488482053588</v>
+        <v>-12.673010588959787</v>
       </c>
       <c r="F504" s="1" t="s">
         <v>22</v>
@@ -13621,19 +13624,19 @@
     </row>
     <row r="505" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B505" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C505">
-        <v>5.7750000000000004</v>
+        <v>6.0419999999999998</v>
       </c>
       <c r="D505">
-        <v>3.7738802780071898</v>
+        <v>5.1105379415961201</v>
       </c>
       <c r="E505">
-        <v>-14.143959265144687</v>
+        <v>-14.91488482053588</v>
       </c>
       <c r="F505" s="1" t="s">
         <v>22</v>
@@ -13644,19 +13647,19 @@
     </row>
     <row r="506" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B506" t="s">
-        <v>475</v>
+        <v>368</v>
       </c>
       <c r="C506">
-        <v>5.1319999999999997</v>
+        <v>5.7750000000000004</v>
       </c>
       <c r="D506">
-        <v>6.3306113837971303</v>
+        <v>3.7738802780071898</v>
       </c>
       <c r="E506">
-        <v>94.85752331046487</v>
+        <v>-14.143959265144687</v>
       </c>
       <c r="F506" s="1" t="s">
         <v>22</v>
@@ -13667,19 +13670,19 @@
     </row>
     <row r="507" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B507" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C507">
-        <v>5.0650000000000004</v>
+        <v>5.1319999999999997</v>
       </c>
       <c r="D507">
-        <v>2.7954168151889203</v>
+        <v>6.3306113837971303</v>
       </c>
       <c r="E507">
-        <v>-15.67261373533278</v>
+        <v>94.85752331046487</v>
       </c>
       <c r="F507" s="1" t="s">
         <v>22</v>
@@ -13690,19 +13693,19 @@
     </row>
     <row r="508" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B508" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C508">
-        <v>5.1879999999999997</v>
+        <v>5.0650000000000004</v>
       </c>
       <c r="D508">
-        <v>4.407976932398884</v>
+        <v>2.7954168151889203</v>
       </c>
       <c r="E508">
-        <v>-3.3241768335749242</v>
+        <v>-15.67261373533278</v>
       </c>
       <c r="F508" s="1" t="s">
         <v>22</v>
@@ -13713,19 +13716,19 @@
     </row>
     <row r="509" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A509" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B509" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C509">
-        <v>5.4189999999999996</v>
+        <v>5.1879999999999997</v>
       </c>
       <c r="D509">
-        <v>5.7839522695566616</v>
+        <v>4.407976932398884</v>
       </c>
       <c r="E509">
-        <v>-7.7280682543894663</v>
+        <v>-3.3241768335749242</v>
       </c>
       <c r="F509" s="1" t="s">
         <v>22</v>
@@ -13736,19 +13739,19 @@
     </row>
     <row r="510" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A510" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B510" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C510">
-        <v>5.4829999999999997</v>
+        <v>5.4189999999999996</v>
       </c>
       <c r="D510">
-        <v>6.3120348655275871</v>
+        <v>5.7839522695566616</v>
       </c>
       <c r="E510">
-        <v>-10.018225732155265</v>
+        <v>-7.7280682543894663</v>
       </c>
       <c r="F510" s="1" t="s">
         <v>22</v>
@@ -13759,19 +13762,19 @@
     </row>
     <row r="511" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A511" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B511" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C511">
-        <v>2.5219999999999998</v>
+        <v>5.4829999999999997</v>
       </c>
       <c r="D511">
-        <v>4.856043498600731</v>
+        <v>6.3120348655275871</v>
       </c>
       <c r="E511">
-        <v>-12.133074207543746</v>
+        <v>-10.018225732155265</v>
       </c>
       <c r="F511" s="1" t="s">
         <v>22</v>
@@ -13782,19 +13785,19 @@
     </row>
     <row r="512" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B512" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C512">
-        <v>2.468</v>
+        <v>2.5219999999999998</v>
       </c>
       <c r="D512">
-        <v>6.8330399532059287</v>
+        <v>4.856043498600731</v>
       </c>
       <c r="E512">
-        <v>-13.136185773863302</v>
+        <v>-12.133074207543746</v>
       </c>
       <c r="F512" s="1" t="s">
         <v>22</v>
@@ -13805,19 +13808,19 @@
     </row>
     <row r="513" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A513" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B513" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C513">
-        <v>5.319</v>
+        <v>2.468</v>
       </c>
       <c r="D513">
-        <v>6.7309326571835175</v>
+        <v>6.8330399532059287</v>
       </c>
       <c r="E513">
-        <v>-14.615798960628902</v>
+        <v>-13.136185773863302</v>
       </c>
       <c r="F513" s="1" t="s">
         <v>22</v>
@@ -13828,19 +13831,19 @@
     </row>
     <row r="514" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A514" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B514" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C514">
-        <v>5.4160000000000004</v>
+        <v>5.319</v>
       </c>
       <c r="D514">
-        <v>6.1865512482601535</v>
+        <v>6.7309326571835175</v>
       </c>
       <c r="E514">
-        <v>-15.003808981450838</v>
+        <v>-14.615798960628902</v>
       </c>
       <c r="F514" s="1" t="s">
         <v>22</v>
@@ -13851,19 +13854,19 @@
     </row>
     <row r="515" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B515" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C515">
-        <v>5.3529999999999998</v>
+        <v>5.4160000000000004</v>
       </c>
       <c r="D515">
-        <v>5.4763906517556675</v>
+        <v>6.1865512482601535</v>
       </c>
       <c r="E515">
-        <v>-14.916658263015243</v>
+        <v>-15.003808981450838</v>
       </c>
       <c r="F515" s="1" t="s">
         <v>22</v>
@@ -13874,19 +13877,19 @@
     </row>
     <row r="516" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A516" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B516" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C516">
-        <v>5.39</v>
+        <v>5.3529999999999998</v>
       </c>
       <c r="D516">
-        <v>5.6046713829787214</v>
+        <v>5.4763906517556675</v>
       </c>
       <c r="E516">
-        <v>122.03298129761575</v>
+        <v>-14.916658263015243</v>
       </c>
       <c r="F516" s="1" t="s">
         <v>22</v>
@@ -13897,19 +13900,19 @@
     </row>
     <row r="517" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A517" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B517" t="s">
-        <v>344</v>
+        <v>484</v>
       </c>
       <c r="C517">
-        <v>5.4980000000000002</v>
+        <v>5.39</v>
       </c>
       <c r="D517">
-        <v>3.0500921527392166</v>
+        <v>5.6046713829787214</v>
       </c>
       <c r="E517">
-        <v>-13.662260465524394</v>
+        <v>122.03298129761575</v>
       </c>
       <c r="F517" s="1" t="s">
         <v>22</v>
@@ -13920,19 +13923,19 @@
     </row>
     <row r="518" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A518" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B518" t="s">
-        <v>486</v>
+        <v>343</v>
       </c>
       <c r="C518">
-        <v>5.0919999999999996</v>
+        <v>5.4980000000000002</v>
       </c>
       <c r="D518">
-        <v>5.868069089861824</v>
+        <v>3.0500921527392166</v>
       </c>
       <c r="E518">
-        <v>0.63824117381073364</v>
+        <v>-13.662260465524394</v>
       </c>
       <c r="F518" s="1" t="s">
         <v>22</v>
@@ -13943,19 +13946,19 @@
     </row>
     <row r="519" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A519" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B519" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C519">
-        <v>5.0030000000000001</v>
+        <v>5.0919999999999996</v>
       </c>
       <c r="D519">
-        <v>4.7993053802209866</v>
+        <v>5.868069089861824</v>
       </c>
       <c r="E519">
-        <v>1.4276061787064052</v>
+        <v>0.63824117381073364</v>
       </c>
       <c r="F519" s="1" t="s">
         <v>22</v>
@@ -13966,19 +13969,19 @@
     </row>
     <row r="520" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B520" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C520">
-        <v>5.125</v>
+        <v>5.0030000000000001</v>
       </c>
       <c r="D520">
-        <v>5.4063793294095417</v>
+        <v>4.7993053802209866</v>
       </c>
       <c r="E520">
-        <v>-3.2374632401697063</v>
+        <v>1.4276061787064052</v>
       </c>
       <c r="F520" s="1" t="s">
         <v>22</v>
@@ -13989,19 +13992,19 @@
     </row>
     <row r="521" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B521" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C521">
-        <v>5.2110000000000003</v>
+        <v>5.125</v>
       </c>
       <c r="D521">
-        <v>4.5931913209354542</v>
+        <v>5.4063793294095417</v>
       </c>
       <c r="E521">
-        <v>-4.0283098022601358</v>
+        <v>-3.2374632401697063</v>
       </c>
       <c r="F521" s="1" t="s">
         <v>22</v>
@@ -14012,19 +14015,19 @@
     </row>
     <row r="522" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B522" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C522">
-        <v>5.3780000000000001</v>
+        <v>5.2110000000000003</v>
       </c>
       <c r="D522">
-        <v>4.8631667000459435</v>
+        <v>4.5931913209354542</v>
       </c>
       <c r="E522">
-        <v>-8.3152297597101459</v>
+        <v>-4.0283098022601358</v>
       </c>
       <c r="F522" s="1" t="s">
         <v>22</v>
@@ -14035,19 +14038,19 @@
     </row>
     <row r="523" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B523" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C523">
-        <v>5.0410000000000004</v>
+        <v>5.3780000000000001</v>
       </c>
       <c r="D523">
-        <v>4.047242938873354</v>
+        <v>4.8631667000459435</v>
       </c>
       <c r="E523">
-        <v>-11.157259137603381</v>
+        <v>-8.3152297597101459</v>
       </c>
       <c r="F523" s="1" t="s">
         <v>22</v>
@@ -14058,19 +14061,19 @@
     </row>
     <row r="524" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B524" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C524">
-        <v>5.3940000000000001</v>
+        <v>5.0410000000000004</v>
       </c>
       <c r="D524">
-        <v>3.0847085705345902</v>
+        <v>4.047242938873354</v>
       </c>
       <c r="E524">
-        <v>-13.048656631364706</v>
+        <v>-11.157259137603381</v>
       </c>
       <c r="F524" s="1" t="s">
         <v>22</v>
@@ -14081,19 +14084,19 @@
     </row>
     <row r="525" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B525" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C525">
-        <v>50.848999999999997</v>
+        <v>5.3940000000000001</v>
       </c>
       <c r="D525">
-        <v>0.46848754850761798</v>
+        <v>3.0847085705345902</v>
       </c>
       <c r="E525">
-        <v>283.09747356051565</v>
+        <v>-13.048656631364706</v>
       </c>
       <c r="F525" s="1" t="s">
         <v>22</v>
@@ -14104,19 +14107,19 @@
     </row>
     <row r="526" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B526" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C526">
-        <v>50.063000000000002</v>
+        <v>50.848999999999997</v>
       </c>
       <c r="D526">
-        <v>0.11372983769903343</v>
+        <v>0.46848754850761798</v>
       </c>
       <c r="E526">
-        <v>7.8827212816513104</v>
+        <v>283.09747356051565</v>
       </c>
       <c r="F526" s="1" t="s">
         <v>22</v>
@@ -14127,19 +14130,19 @@
     </row>
     <row r="527" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B527" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C527">
-        <v>50.42</v>
+        <v>50.063000000000002</v>
       </c>
       <c r="D527">
-        <v>0.16899243360318777</v>
+        <v>0.11372983769903343</v>
       </c>
       <c r="E527">
-        <v>2.5504859560486537</v>
+        <v>7.8827212816513104</v>
       </c>
       <c r="F527" s="1" t="s">
         <v>22</v>
@@ -14150,19 +14153,19 @@
     </row>
     <row r="528" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B528" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C528">
-        <v>50.180999999999997</v>
+        <v>50.42</v>
       </c>
       <c r="D528">
-        <v>0.16462556110230422</v>
+        <v>0.16899243360318777</v>
       </c>
       <c r="E528">
-        <v>0.45736079978889776</v>
+        <v>2.5504859560486537</v>
       </c>
       <c r="F528" s="1" t="s">
         <v>22</v>
@@ -14173,19 +14176,19 @@
     </row>
     <row r="529" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B529" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C529">
-        <v>50.21</v>
+        <v>50.180999999999997</v>
       </c>
       <c r="D529">
-        <v>0.14872666061812412</v>
+        <v>0.16462556110230422</v>
       </c>
       <c r="E529">
-        <v>1.0678595207323056</v>
+        <v>0.45736079978889776</v>
       </c>
       <c r="F529" s="1" t="s">
         <v>22</v>
@@ -14196,19 +14199,19 @@
     </row>
     <row r="530" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B530" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C530">
-        <v>50.39</v>
+        <v>50.21</v>
       </c>
       <c r="D530">
-        <v>0.11735055434989371</v>
+        <v>0.14872666061812412</v>
       </c>
       <c r="E530">
-        <v>0.69574263646376266</v>
+        <v>1.0678595207323056</v>
       </c>
       <c r="F530" s="1" t="s">
         <v>22</v>
@@ -14219,19 +14222,19 @@
     </row>
     <row r="531" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B531" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C531">
-        <v>50.738999999999997</v>
+        <v>50.39</v>
       </c>
       <c r="D531">
-        <v>9.335011542476164E-2</v>
+        <v>0.11735055434989371</v>
       </c>
       <c r="E531">
-        <v>4.0231822509745605</v>
+        <v>0.69574263646376266</v>
       </c>
       <c r="F531" s="1" t="s">
         <v>22</v>
@@ -14242,19 +14245,19 @@
     </row>
     <row r="532" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B532" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C532">
-        <v>50.393000000000001</v>
+        <v>50.738999999999997</v>
       </c>
       <c r="D532">
-        <v>0.10115056224064807</v>
+        <v>9.335011542476164E-2</v>
       </c>
       <c r="E532">
-        <v>6.4650661718476137</v>
+        <v>4.0231822509745605</v>
       </c>
       <c r="F532" s="1" t="s">
         <v>22</v>
@@ -14265,19 +14268,19 @@
     </row>
     <row r="533" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B533" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C533">
-        <v>50.953000000000003</v>
+        <v>50.393000000000001</v>
       </c>
       <c r="D533">
-        <v>0.11720331685269754</v>
+        <v>0.10115056224064807</v>
       </c>
       <c r="E533">
-        <v>5.4061542179158373</v>
+        <v>6.4650661718476137</v>
       </c>
       <c r="F533" s="1" t="s">
         <v>22</v>
@@ -14288,19 +14291,19 @@
     </row>
     <row r="534" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B534" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C534">
-        <v>50.082999999999998</v>
+        <v>50.953000000000003</v>
       </c>
       <c r="D534">
-        <v>0.1094889496320548</v>
+        <v>0.11720331685269754</v>
       </c>
       <c r="E534">
-        <v>9.049219349308057</v>
+        <v>5.4061542179158373</v>
       </c>
       <c r="F534" s="1" t="s">
         <v>22</v>
@@ -14311,19 +14314,19 @@
     </row>
     <row r="535" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B535" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C535">
-        <v>50.77</v>
+        <v>50.082999999999998</v>
       </c>
       <c r="D535">
-        <v>0.11012970243310102</v>
+        <v>0.1094889496320548</v>
       </c>
       <c r="E535">
-        <v>18.480608849477061</v>
+        <v>9.049219349308057</v>
       </c>
       <c r="F535" s="1" t="s">
         <v>22</v>
@@ -14334,19 +14337,19 @@
     </row>
     <row r="536" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B536" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="C536">
-        <v>50.348999999999997</v>
+        <v>50.77</v>
       </c>
       <c r="D536">
-        <v>0.19383162441857771</v>
+        <v>0.11012970243310102</v>
       </c>
       <c r="E536">
-        <v>-20.162879626459944</v>
+        <v>18.480608849477061</v>
       </c>
       <c r="F536" s="1" t="s">
         <v>22</v>
@@ -14357,19 +14360,19 @@
     </row>
     <row r="537" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B537" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C537">
-        <v>3.9460000000000002</v>
+        <v>50.348999999999997</v>
       </c>
       <c r="D537">
-        <v>3.9248866025641149</v>
+        <v>0.19383162441857771</v>
       </c>
       <c r="E537">
-        <v>-16.807061461265931</v>
+        <v>-20.162879626459944</v>
       </c>
       <c r="F537" s="1" t="s">
         <v>22</v>
@@ -14380,19 +14383,19 @@
     </row>
     <row r="538" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B538" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C538">
-        <v>3.907</v>
+        <v>3.9460000000000002</v>
       </c>
       <c r="D538">
-        <v>7.055850183117923</v>
+        <v>3.9248866025641149</v>
       </c>
       <c r="E538">
-        <v>-16.472061999050638</v>
+        <v>-16.807061461265931</v>
       </c>
       <c r="F538" s="1" t="s">
         <v>22</v>
@@ -14403,19 +14406,19 @@
     </row>
     <row r="539" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B539" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C539">
-        <v>4.8550000000000004</v>
+        <v>3.907</v>
       </c>
       <c r="D539">
-        <v>5.160277946259213</v>
+        <v>7.055850183117923</v>
       </c>
       <c r="E539">
-        <v>-16.224867813732786</v>
+        <v>-16.472061999050638</v>
       </c>
       <c r="F539" s="1" t="s">
         <v>22</v>
@@ -14426,19 +14429,19 @@
     </row>
     <row r="540" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B540" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C540">
-        <v>4.4029999999999996</v>
+        <v>4.8550000000000004</v>
       </c>
       <c r="D540">
-        <v>6.2402601428622884</v>
+        <v>5.160277946259213</v>
       </c>
       <c r="E540">
-        <v>-15.686440632218819</v>
+        <v>-16.224867813732786</v>
       </c>
       <c r="F540" s="1" t="s">
         <v>22</v>
@@ -14449,19 +14452,19 @@
     </row>
     <row r="541" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B541" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C541">
-        <v>5.4219999999999997</v>
+        <v>4.4029999999999996</v>
       </c>
       <c r="D541">
-        <v>4.7703912405862443</v>
+        <v>6.2402601428622884</v>
       </c>
       <c r="E541">
-        <v>-15.243286402780903</v>
+        <v>-15.686440632218819</v>
       </c>
       <c r="F541" s="1" t="s">
         <v>22</v>
@@ -14472,19 +14475,19 @@
     </row>
     <row r="542" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B542" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C542">
-        <v>1.8360000000000001</v>
+        <v>5.4219999999999997</v>
       </c>
       <c r="D542">
-        <v>8.5376244547654405</v>
+        <v>4.7703912405862443</v>
       </c>
       <c r="E542">
-        <v>-16.332458623680839</v>
+        <v>-15.243286402780903</v>
       </c>
       <c r="F542" s="1" t="s">
         <v>22</v>
@@ -14495,19 +14498,19 @@
     </row>
     <row r="543" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B543" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C543">
-        <v>5.1070000000000002</v>
+        <v>1.8360000000000001</v>
       </c>
       <c r="D543">
-        <v>5.2129376526686295</v>
+        <v>8.5376244547654405</v>
       </c>
       <c r="E543">
-        <v>-17.130922287844811</v>
+        <v>-16.332458623680839</v>
       </c>
       <c r="F543" s="1" t="s">
         <v>22</v>
@@ -14518,19 +14521,19 @@
     </row>
     <row r="544" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B544" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C544">
-        <v>1.958</v>
+        <v>5.1070000000000002</v>
       </c>
       <c r="D544">
-        <v>12.180846336703958</v>
+        <v>5.2129376526686295</v>
       </c>
       <c r="E544">
-        <v>-16.63068662845199</v>
+        <v>-17.130922287844811</v>
       </c>
       <c r="F544" s="1" t="s">
         <v>22</v>
@@ -14541,19 +14544,19 @@
     </row>
     <row r="545" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B545" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C545">
-        <v>4.2069999999999999</v>
+        <v>1.958</v>
       </c>
       <c r="D545">
-        <v>4.7974629683845427</v>
+        <v>12.180846336703958</v>
       </c>
       <c r="E545">
-        <v>-15.984753492099873</v>
+        <v>-16.63068662845199</v>
       </c>
       <c r="F545" s="1" t="s">
         <v>22</v>
@@ -14564,19 +14567,19 @@
     </row>
     <row r="546" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B546" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C546">
-        <v>4.298</v>
+        <v>4.2069999999999999</v>
       </c>
       <c r="D546">
-        <v>4.8281581291590454</v>
+        <v>4.7974629683845427</v>
       </c>
       <c r="E546">
-        <v>-16.139292284716888</v>
+        <v>-15.984753492099873</v>
       </c>
       <c r="F546" s="1" t="s">
         <v>22</v>
@@ -14587,19 +14590,19 @@
     </row>
     <row r="547" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B547" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C547">
-        <v>4.8739999999999997</v>
+        <v>4.298</v>
       </c>
       <c r="D547">
-        <v>5.4481521639305699</v>
+        <v>4.8281581291590454</v>
       </c>
       <c r="E547">
-        <v>-16.209768105013161</v>
+        <v>-16.139292284716888</v>
       </c>
       <c r="F547" s="1" t="s">
         <v>22</v>
@@ -14610,19 +14613,19 @@
     </row>
     <row r="548" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B548" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C548">
-        <v>5.2069999999999999</v>
+        <v>4.8739999999999997</v>
       </c>
       <c r="D548">
-        <v>4.1327742326003358</v>
+        <v>5.4481521639305699</v>
       </c>
       <c r="E548">
-        <v>-16.091731247649712</v>
+        <v>-16.209768105013161</v>
       </c>
       <c r="F548" s="1" t="s">
         <v>22</v>
@@ -14633,19 +14636,19 @@
     </row>
     <row r="549" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B549" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C549">
-        <v>5.2480000000000002</v>
+        <v>5.2069999999999999</v>
       </c>
       <c r="D549">
-        <v>6.7583751773441447</v>
+        <v>4.1327742326003358</v>
       </c>
       <c r="E549">
-        <v>-17.125431543143655</v>
+        <v>-16.091731247649712</v>
       </c>
       <c r="F549" s="1" t="s">
         <v>22</v>
@@ -14656,19 +14659,19 @@
     </row>
     <row r="550" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B550" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C550">
-        <v>5.8479999999999999</v>
+        <v>5.2480000000000002</v>
       </c>
       <c r="D550">
-        <v>2.8842023815657267</v>
+        <v>6.7583751773441447</v>
       </c>
       <c r="E550">
-        <v>-16.51369848355796</v>
+        <v>-17.125431543143655</v>
       </c>
       <c r="F550" s="1" t="s">
         <v>22</v>
@@ -14679,19 +14682,19 @@
     </row>
     <row r="551" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B551" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C551">
-        <v>4.41</v>
+        <v>5.8479999999999999</v>
       </c>
       <c r="D551">
-        <v>2.9594203781449888</v>
+        <v>2.8842023815657267</v>
       </c>
       <c r="E551">
-        <v>-15.698364261780727</v>
+        <v>-16.51369848355796</v>
       </c>
       <c r="F551" s="1" t="s">
         <v>22</v>
@@ -14702,19 +14705,19 @@
     </row>
     <row r="552" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B552" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C552">
-        <v>3.3039999999999998</v>
+        <v>4.41</v>
       </c>
       <c r="D552">
-        <v>3.6087079090129808</v>
+        <v>2.9594203781449888</v>
       </c>
       <c r="E552">
-        <v>-15.629708626246387</v>
+        <v>-15.698364261780727</v>
       </c>
       <c r="F552" s="1" t="s">
         <v>22</v>
@@ -14725,19 +14728,19 @@
     </row>
     <row r="553" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B553" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C553">
-        <v>5.2889999999999997</v>
+        <v>3.3039999999999998</v>
       </c>
       <c r="D553">
-        <v>4.1832933494231925</v>
+        <v>3.6087079090129808</v>
       </c>
       <c r="E553">
-        <v>-16.120846088384106</v>
+        <v>-15.629708626246387</v>
       </c>
       <c r="F553" s="1" t="s">
         <v>22</v>
@@ -14748,19 +14751,19 @@
     </row>
     <row r="554" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B554" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C554">
-        <v>5.415</v>
+        <v>5.2889999999999997</v>
       </c>
       <c r="D554">
-        <v>6.7720280320023862</v>
+        <v>4.1832933494231925</v>
       </c>
       <c r="E554">
-        <v>-17.734510725458723</v>
+        <v>-16.120846088384106</v>
       </c>
       <c r="F554" s="1" t="s">
         <v>22</v>
@@ -14771,19 +14774,19 @@
     </row>
     <row r="555" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B555" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C555">
-        <v>5.1970000000000001</v>
+        <v>5.415</v>
       </c>
       <c r="D555">
-        <v>4.7645547489324898</v>
+        <v>6.7720280320023862</v>
       </c>
       <c r="E555">
-        <v>-15.91016898748053</v>
+        <v>-17.734510725458723</v>
       </c>
       <c r="F555" s="1" t="s">
         <v>22</v>
@@ -14794,19 +14797,19 @@
     </row>
     <row r="556" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B556" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C556">
-        <v>3.0630000000000002</v>
+        <v>5.1970000000000001</v>
       </c>
       <c r="D556">
-        <v>5.7387985580630216</v>
+        <v>4.7645547489324898</v>
       </c>
       <c r="E556">
-        <v>-15.842674874063443</v>
+        <v>-15.91016898748053</v>
       </c>
       <c r="F556" s="1" t="s">
         <v>22</v>
@@ -14817,19 +14820,19 @@
     </row>
     <row r="557" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B557" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C557">
-        <v>2.7909999999999999</v>
+        <v>3.0630000000000002</v>
       </c>
       <c r="D557">
-        <v>7.0825915302684699</v>
+        <v>5.7387985580630216</v>
       </c>
       <c r="E557">
-        <v>-15.584178687591127</v>
+        <v>-15.842674874063443</v>
       </c>
       <c r="F557" s="1" t="s">
         <v>22</v>
@@ -14840,19 +14843,19 @@
     </row>
     <row r="558" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B558" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C558">
-        <v>4.3769999999999998</v>
+        <v>2.7909999999999999</v>
       </c>
       <c r="D558">
-        <v>5.6006739898339859</v>
+        <v>7.0825915302684699</v>
       </c>
       <c r="E558">
-        <v>-16.402275740195275</v>
+        <v>-15.584178687591127</v>
       </c>
       <c r="F558" s="1" t="s">
         <v>22</v>
@@ -14863,42 +14866,42 @@
     </row>
     <row r="559" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B559" t="s">
-        <v>504</v>
+        <v>528</v>
       </c>
       <c r="C559">
-        <v>5.15</v>
+        <v>4.3769999999999998</v>
       </c>
       <c r="D559">
-        <v>8.0918963800809394</v>
+        <v>5.6006739898339859</v>
       </c>
       <c r="E559">
-        <v>-11.251690952265887</v>
+        <v>-16.402275740195275</v>
       </c>
       <c r="F559" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G559" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="560" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B560" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C560">
-        <v>5.3579999999999997</v>
+        <v>5.15</v>
       </c>
       <c r="D560">
-        <v>7.0705549894030755</v>
+        <v>8.0918963800809394</v>
       </c>
       <c r="E560">
-        <v>-18.538649946373564</v>
+        <v>-11.251690952265887</v>
       </c>
       <c r="F560" s="1" t="s">
         <v>22</v>
@@ -14909,24 +14912,47 @@
     </row>
     <row r="561" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B561" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C561">
+        <v>5.3579999999999997</v>
+      </c>
+      <c r="D561">
+        <v>7.0705549894030755</v>
+      </c>
+      <c r="E561">
+        <v>-18.538649946373564</v>
+      </c>
+      <c r="F561" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G561" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="562" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A562" t="s">
+        <v>394</v>
+      </c>
+      <c r="B562" t="s">
+        <v>505</v>
+      </c>
+      <c r="C562">
         <v>5.4829999999999997</v>
       </c>
-      <c r="D561">
+      <c r="D562">
         <v>6.7186534018607302</v>
       </c>
-      <c r="E561">
+      <c r="E562">
         <v>17.235074277640731</v>
       </c>
-      <c r="F561" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G561" t="b">
+      <c r="F562" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G562" t="b">
         <v>0</v>
       </c>
     </row>
